--- a/Microservices/sighaCalco.Integration/templates/Template_1.xlsx
+++ b/Microservices/sighaCalco.Integration/templates/Template_1.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.eusse\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juan.eusse\source\repos\sighaCalco\Microservices\sighaCalco.Integration\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA24FED6-A6A5-438D-A194-ECA1ED07EDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771271D7-B52F-4B30-B03F-DB9993E49EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-50" windowWidth="19420" windowHeight="11500" tabRatio="940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ingresos" sheetId="1" r:id="rId1"/>
+    <sheet name="Cambios de Maestro" sheetId="3" r:id="rId2"/>
+    <sheet name="Modificaciones de Salario" sheetId="7" r:id="rId3"/>
+    <sheet name="Retiros" sheetId="8" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_05">#REF!</definedName>
     <definedName name="_08">#REF!</definedName>
     <definedName name="_11">#REF!</definedName>
     <definedName name="_13">#REF!</definedName>
     <definedName name="_15">#REF!</definedName>
+    <definedName name="_169" localSheetId="3">'[1]Listados Codigos'!$P$4:$P$36</definedName>
     <definedName name="_169">#REF!</definedName>
     <definedName name="_17">#REF!</definedName>
     <definedName name="_18">#REF!</definedName>
@@ -54,6 +61,7 @@
     <definedName name="_95">#REF!</definedName>
     <definedName name="_97">#REF!</definedName>
     <definedName name="_99">#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cambios de Maestro'!$A$1:$D$1</definedName>
     <definedName name="COLOMBIA">#REF!</definedName>
     <definedName name="CURAZAO">#REF!</definedName>
     <definedName name="ECUADOR">#REF!</definedName>
@@ -83,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="175">
   <si>
     <t>ojos</t>
   </si>
@@ -94,6 +102,12 @@
     <t>escalafon</t>
   </si>
   <si>
+    <t>CARGO</t>
+  </si>
+  <si>
+    <t>EMPLEADO</t>
+  </si>
+  <si>
     <t>empleado</t>
   </si>
   <si>
@@ -407,13 +421,208 @@
   </si>
   <si>
     <t>municipio_resid</t>
+  </si>
+  <si>
+    <t>Empleado</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Campo a Modificar</t>
+  </si>
+  <si>
+    <t>Dato Nuevo</t>
+  </si>
+  <si>
+    <t>Fecha de Cambio</t>
+  </si>
+  <si>
+    <t>NOMBRE COMPLETO</t>
+  </si>
+  <si>
+    <t>OBSERVACIONES</t>
+  </si>
+  <si>
+    <t>FECHA DE INGRESO</t>
+  </si>
+  <si>
+    <t>FECHA CAMBIO SALARIO</t>
+  </si>
+  <si>
+    <t>SALARIO ACTUAL</t>
+  </si>
+  <si>
+    <t>SALARIO NUEVO</t>
+  </si>
+  <si>
+    <t>TIPO DE SALARIO NUEVO</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Codigo</t>
+  </si>
+  <si>
+    <t>PRORROGA</t>
+  </si>
+  <si>
+    <t>DX</t>
+  </si>
+  <si>
+    <t>TIPO INCAP</t>
+  </si>
+  <si>
+    <t>TOTAL DIAS</t>
+  </si>
+  <si>
+    <t>FECHA FIN</t>
+  </si>
+  <si>
+    <t>FECHA INICIO</t>
+  </si>
+  <si>
+    <t># INCAPAC</t>
+  </si>
+  <si>
+    <t>DESCRIPC CONCEPTO</t>
+  </si>
+  <si>
+    <t>PDV</t>
+  </si>
+  <si>
+    <t>DISTRIBUCION</t>
+  </si>
+  <si>
+    <t>HORA LACTANCIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SALARIO ORDINARIO H</t>
+  </si>
+  <si>
+    <t>SALIDA TEMPRANA POR SOLICITD COLABORADOR</t>
+  </si>
+  <si>
+    <t>RECARGO FESTIVO NOCTURNO</t>
+  </si>
+  <si>
+    <t>FESTIVO</t>
+  </si>
+  <si>
+    <t>HORA CAPACITACION</t>
+  </si>
+  <si>
+    <t>RECARGO DOMINCAL DIURNO</t>
+  </si>
+  <si>
+    <t>HORA EXTRA DIURNA FESTIVO</t>
+  </si>
+  <si>
+    <t>HORA EXTRA NOCTURNA FESTIVO</t>
+  </si>
+  <si>
+    <t>EXTRA NOCTURA DOMINICAL</t>
+  </si>
+  <si>
+    <t>EXTRA DIURNA DOMINICAL</t>
+  </si>
+  <si>
+    <t>RECARGO NOCTURNO DOMINICAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECARGO NOCTURNO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HORA EXTRA NOCTURNA ORDINARIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HORA EXTRA DIURNA ORDINARIA </t>
+  </si>
+  <si>
+    <t>Fecha de Marcacion</t>
+  </si>
+  <si>
+    <t>Punto de venta</t>
+  </si>
+  <si>
+    <t>MOTIVO</t>
+  </si>
+  <si>
+    <t>FECHA DE RETIRO</t>
+  </si>
+  <si>
+    <t>NOMBRE</t>
+  </si>
+  <si>
+    <t>CEDULA</t>
+  </si>
+  <si>
+    <t>Deducciones</t>
+  </si>
+  <si>
+    <t>Incapacidades</t>
+  </si>
+  <si>
+    <t>Ausentismos</t>
+  </si>
+  <si>
+    <t>0299</t>
+  </si>
+  <si>
+    <t>0009</t>
+  </si>
+  <si>
+    <t>0828</t>
+  </si>
+  <si>
+    <t>0260</t>
+  </si>
+  <si>
+    <t>0239</t>
+  </si>
+  <si>
+    <t>1312</t>
+  </si>
+  <si>
+    <t>0251</t>
+  </si>
+  <si>
+    <t>0275</t>
+  </si>
+  <si>
+    <t>0274</t>
+  </si>
+  <si>
+    <t>0270</t>
+  </si>
+  <si>
+    <t>0271</t>
+  </si>
+  <si>
+    <t>0257</t>
+  </si>
+  <si>
+    <t>0204</t>
+  </si>
+  <si>
+    <t>0202</t>
+  </si>
+  <si>
+    <t>0200</t>
+  </si>
+  <si>
+    <t>Datos Generales</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,12 +665,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -477,6 +693,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -504,8 +726,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -528,13 +762,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -554,32 +823,37 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -587,6 +861,21 @@
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -647,6 +936,525 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Listados Codigos"/>
+      <sheetName val="Maestro Activos"/>
+      <sheetName val="Ingresos"/>
+      <sheetName val="Cambios de Maestro"/>
+      <sheetName val="Prorrogas"/>
+      <sheetName val="Modificaciones de Salario"/>
+      <sheetName val="Incapacidades"/>
+      <sheetName val="Vacaciones"/>
+      <sheetName val="Licencias y Permisos"/>
+      <sheetName val="Horas Extras y Recargos"/>
+      <sheetName val="Devengos Ocasionales"/>
+      <sheetName val="Devengos Fijos"/>
+      <sheetName val="Deducciones Ocasionales"/>
+      <sheetName val="Deducciones Fijas"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="EB2" t="str">
+            <v>DESCRIPCION CONCEPTO</v>
+          </cell>
+          <cell r="EC2" t="str">
+            <v>CONCEPTO SINERGY</v>
+          </cell>
+          <cell r="EG2" t="str">
+            <v>DESCRIPCION CONCEPTO</v>
+          </cell>
+          <cell r="EH2" t="str">
+            <v>CONCEPTO SINERGY</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="EB3" t="str">
+            <v>LICENCIA REMUNERADA</v>
+          </cell>
+          <cell r="EC3" t="str">
+            <v>0700</v>
+          </cell>
+          <cell r="EG3" t="str">
+            <v>ADICIONAL FUNERARIA</v>
+          </cell>
+          <cell r="EH3">
+            <v>2729</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="P4" t="str">
+            <v>05 - ANTIOQUIA</v>
+          </cell>
+          <cell r="EB4" t="str">
+            <v>PERMISO REMUNERADO</v>
+          </cell>
+          <cell r="EC4" t="str">
+            <v>0800</v>
+          </cell>
+          <cell r="EG4" t="str">
+            <v>AHORRO COOPANTEX</v>
+          </cell>
+          <cell r="EH4">
+            <v>2694</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="P5" t="str">
+            <v>08 - ATLANTICO</v>
+          </cell>
+          <cell r="EB5" t="str">
+            <v>PERMISO NO REMUNERADO</v>
+          </cell>
+          <cell r="EC5" t="str">
+            <v>0801</v>
+          </cell>
+          <cell r="EG5" t="str">
+            <v>AHORRO COOPERATIVA BELEN</v>
+          </cell>
+          <cell r="EH5">
+            <v>2689</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="P6" t="str">
+            <v>11 - BOGOTA</v>
+          </cell>
+          <cell r="EB6" t="str">
+            <v>SUSPENSION DISCIPLINARIA</v>
+          </cell>
+          <cell r="EC6" t="str">
+            <v>0802</v>
+          </cell>
+          <cell r="EG6" t="str">
+            <v>AHORRO COOPETRABAN</v>
+          </cell>
+          <cell r="EH6">
+            <v>2697</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="P7" t="str">
+            <v>13 - BOLIVAR</v>
+          </cell>
+          <cell r="EB7" t="str">
+            <v>LICENCIA POR LUTO</v>
+          </cell>
+          <cell r="EC7" t="str">
+            <v>0803</v>
+          </cell>
+          <cell r="EG7" t="str">
+            <v>AHORRO COTRAFA</v>
+          </cell>
+          <cell r="EH7">
+            <v>2726</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="P8" t="str">
+            <v>15 - BOYACA</v>
+          </cell>
+          <cell r="EB8" t="str">
+            <v>LICENCIA MATRIMONIO</v>
+          </cell>
+          <cell r="EC8" t="str">
+            <v>0805</v>
+          </cell>
+          <cell r="EG8" t="str">
+            <v>COBRO PREPAGADA COLMEDICAS</v>
+          </cell>
+          <cell r="EH8">
+            <v>3551</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="P9" t="str">
+            <v>17 - CALDAS</v>
+          </cell>
+          <cell r="EB9" t="str">
+            <v>CALMIDAD DOMESTICA</v>
+          </cell>
+          <cell r="EC9" t="str">
+            <v>0806</v>
+          </cell>
+          <cell r="EG9" t="str">
+            <v>COBRO PREPAGADA MEDISANITAS</v>
+          </cell>
+          <cell r="EH9">
+            <v>2672</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="P10" t="str">
+            <v>18 - CAQUETA</v>
+          </cell>
+          <cell r="EB10" t="str">
+            <v>DIA FAMILIA</v>
+          </cell>
+          <cell r="EC10" t="str">
+            <v>0807</v>
+          </cell>
+          <cell r="EG10" t="str">
+            <v>COOPCAFAM AHORRO</v>
+          </cell>
+          <cell r="EH10">
+            <v>2679</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="P11" t="str">
+            <v>19 - CAUCA</v>
+          </cell>
+          <cell r="EB11" t="str">
+            <v>GLOBAL INCAPACIDAD NO PRESENTADA</v>
+          </cell>
+          <cell r="EC11" t="str">
+            <v>0812</v>
+          </cell>
+          <cell r="EG11" t="str">
+            <v>COOPERATIVA DE CREDITO Y SERVICIO COMUNIDAD</v>
+          </cell>
+          <cell r="EH11">
+            <v>2737</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="P12" t="str">
+            <v>20 - CESAR</v>
+          </cell>
+          <cell r="EB12" t="str">
+            <v>DIA VOTACION</v>
+          </cell>
+          <cell r="EC12" t="str">
+            <v>0813</v>
+          </cell>
+          <cell r="EG12" t="str">
+            <v>CUOTA PLAN ODONTOLOGICO</v>
+          </cell>
+          <cell r="EH12">
+            <v>2696</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="P13" t="str">
+            <v>23 - CORDOBA</v>
+          </cell>
+          <cell r="EB13" t="str">
+            <v>HORAS VOTACION</v>
+          </cell>
+          <cell r="EC13" t="str">
+            <v>0814</v>
+          </cell>
+          <cell r="EG13" t="str">
+            <v>CXP NOMINA</v>
+          </cell>
+          <cell r="EH13">
+            <v>2685</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="P14" t="str">
+            <v>25 - CUNDINAMARCA</v>
+          </cell>
+          <cell r="EB14" t="str">
+            <v>PERDIDA DESCANSO</v>
+          </cell>
+          <cell r="EC14" t="str">
+            <v>0815</v>
+          </cell>
+          <cell r="EG14" t="str">
+            <v>DAFUTURO AHORRO</v>
+          </cell>
+          <cell r="EH14">
+            <v>2684</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="P15" t="str">
+            <v>27 - CHOCO</v>
+          </cell>
+          <cell r="EB15" t="str">
+            <v>EXTENSION LICENCIA MATERNIDAD</v>
+          </cell>
+          <cell r="EC15" t="str">
+            <v>0822</v>
+          </cell>
+          <cell r="EG15" t="str">
+            <v>DESCUENTO ADICIONAL PLAN COMPLEMENTARIO</v>
+          </cell>
+          <cell r="EH15">
+            <v>2673</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="P16" t="str">
+            <v>41 - HUILA</v>
+          </cell>
+          <cell r="EB16" t="str">
+            <v>VACACIONES</v>
+          </cell>
+          <cell r="EC16" t="str">
+            <v>0900</v>
+          </cell>
+          <cell r="EG16" t="str">
+            <v>DESCUENTO AFC</v>
+          </cell>
+          <cell r="EH16">
+            <v>2639</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="P17" t="str">
+            <v>44 - LA GUAJIRA</v>
+          </cell>
+          <cell r="EB17" t="str">
+            <v>VACACIONES COMPENSADAS</v>
+          </cell>
+          <cell r="EC17" t="str">
+            <v>0902</v>
+          </cell>
+          <cell r="EG17" t="str">
+            <v>DESCUENTO BENEFICIARIOS COLSANITAS</v>
+          </cell>
+          <cell r="EH17">
+            <v>2671</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="P18" t="str">
+            <v>47 - MAGDALENA</v>
+          </cell>
+          <cell r="EB18" t="str">
+            <v>AUSENCIA SIN JUSTA CAUSA</v>
+          </cell>
+          <cell r="EC18">
+            <v>1681</v>
+          </cell>
+          <cell r="EG18" t="str">
+            <v>DESCUENTO BENEFICIARIOS PREPAGADA COLMED</v>
+          </cell>
+          <cell r="EH18">
+            <v>2670</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="P19" t="str">
+            <v>50 - META</v>
+          </cell>
+          <cell r="EB19" t="str">
+            <v>ANT.VAC.COVID19</v>
+          </cell>
+          <cell r="EC19">
+            <v>1901</v>
+          </cell>
+          <cell r="EG19" t="str">
+            <v>DESCUENTO CELULAR</v>
+          </cell>
+          <cell r="EH19">
+            <v>2725</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="P20" t="str">
+            <v>52 - NARIÑO</v>
+          </cell>
+          <cell r="EB20" t="str">
+            <v>LICENCIA NO REMUNERADA</v>
+          </cell>
+          <cell r="EC20">
+            <v>2110</v>
+          </cell>
+          <cell r="EG20" t="str">
+            <v>FONDO DE EMPLEADOS DE TELEFÓNICA COLOMBIA</v>
+          </cell>
+          <cell r="EH20">
+            <v>2789</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="P21" t="str">
+            <v>54 - N. SANTANDER</v>
+          </cell>
+          <cell r="EG21" t="str">
+            <v>FUNERARIA BENEFICIARIOS</v>
+          </cell>
+          <cell r="EH21">
+            <v>2665</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="P22" t="str">
+            <v>63 - QUINDIO</v>
+          </cell>
+          <cell r="EG22" t="str">
+            <v>PAGO AUXILIO FUNERARIO EMPLEADOS</v>
+          </cell>
+          <cell r="EH22">
+            <v>2722</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="P23" t="str">
+            <v>66 - RISARALDA</v>
+          </cell>
+          <cell r="EG23" t="str">
+            <v>PAGO PLAN COMPLEMENTARIO</v>
+          </cell>
+          <cell r="EH23">
+            <v>2664</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="P24" t="str">
+            <v>68 - SANTANDER</v>
+          </cell>
+          <cell r="EG24" t="str">
+            <v>PAGO PREPAGADA COLMEDICA</v>
+          </cell>
+          <cell r="EH24">
+            <v>3550</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="P25" t="str">
+            <v>70 - SUCRE</v>
+          </cell>
+          <cell r="EG25" t="str">
+            <v>PAGO PREPAGADA COLSANITAS</v>
+          </cell>
+          <cell r="EH25">
+            <v>2602</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="P26" t="str">
+            <v>73 - TOLIMA</v>
+          </cell>
+          <cell r="EG26" t="str">
+            <v>PAGO PREPAGADA MEDISANITAS</v>
+          </cell>
+          <cell r="EH26">
+            <v>2603</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="P27" t="str">
+            <v>76 - VALLE DEL CAUCA</v>
+          </cell>
+          <cell r="EG27" t="str">
+            <v>RETENCION EN LA FUENTE VOLUNTARIA</v>
+          </cell>
+          <cell r="EH27">
+            <v>2309</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="P28" t="str">
+            <v>81 - ARAUCA</v>
+          </cell>
+          <cell r="EG28" t="str">
+            <v>SEGURO SURAMERICANA</v>
+          </cell>
+          <cell r="EH28">
+            <v>2652</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="P29" t="str">
+            <v>85 - CASANARE</v>
+          </cell>
+          <cell r="EG29" t="str">
+            <v>SEGURO VIDA COLSEGUROS</v>
+          </cell>
+          <cell r="EH29">
+            <v>2735</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="P30" t="str">
+            <v>86 - PUTUMAYO</v>
+          </cell>
+          <cell r="EG30" t="str">
+            <v>TARJETA DORADA</v>
+          </cell>
+          <cell r="EH30">
+            <v>2695</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="P31" t="str">
+            <v>88 - SAN ANDRES</v>
+          </cell>
+          <cell r="EG31" t="str">
+            <v>VOLUNTARIAS SKANDIA</v>
+          </cell>
+          <cell r="EH31">
+            <v>2615</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="P32" t="str">
+            <v>91 - AMAZONAS</v>
+          </cell>
+          <cell r="EG32" t="str">
+            <v>VOLUNTARIOS COLFONDOS</v>
+          </cell>
+          <cell r="EH32">
+            <v>2611</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="P33" t="str">
+            <v>94 - GUAINIA</v>
+          </cell>
+          <cell r="EG33" t="str">
+            <v>VOLUNTARIOS PROTECCION</v>
+          </cell>
+          <cell r="EH33">
+            <v>2614</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="P34" t="str">
+            <v>95 - GUAVIARE</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="P35" t="str">
+            <v>97 - VAUPES</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="P36" t="str">
+            <v>99 - VICHADA</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -914,397 +1722,397 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:DD50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" customWidth="1"/>
-    <col min="17" max="20" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.81640625" customWidth="1"/>
+    <col min="13" max="13" width="13.81640625" customWidth="1"/>
+    <col min="16" max="16" width="18.81640625" customWidth="1"/>
+    <col min="17" max="20" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="18" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="16" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.42578125" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" customWidth="1"/>
-    <col min="29" max="29" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="41.5703125" customWidth="1"/>
-    <col min="32" max="32" width="15.28515625" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" customWidth="1"/>
-    <col min="34" max="34" width="20.28515625" customWidth="1"/>
+    <col min="27" max="27" width="15.453125" customWidth="1"/>
+    <col min="28" max="28" width="15.1796875" customWidth="1"/>
+    <col min="29" max="29" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="41.54296875" customWidth="1"/>
+    <col min="32" max="32" width="15.26953125" customWidth="1"/>
+    <col min="33" max="33" width="13.453125" customWidth="1"/>
+    <col min="34" max="34" width="20.26953125" customWidth="1"/>
     <col min="35" max="35" width="25" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="17.54296875" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="13" customWidth="1"/>
     <col min="43" max="43" width="19" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="19.7109375" customWidth="1"/>
-    <col min="52" max="52" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.7265625" customWidth="1"/>
+    <col min="52" max="52" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="17" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="75" max="75" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="77" max="77" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="78" max="78" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="77" max="77" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="78" max="78" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="79" max="79" width="31" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="14.42578125" customWidth="1"/>
-    <col min="81" max="81" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="84" max="84" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="85" max="85" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="14.453125" customWidth="1"/>
+    <col min="81" max="81" width="20.81640625" bestFit="1" customWidth="1"/>
+    <col min="82" max="82" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="83" max="83" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="84" max="84" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="85" max="85" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="88" max="88" width="32" customWidth="1"/>
-    <col min="89" max="89" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="90" max="90" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="92" max="92" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="94" max="94" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="96" max="96" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="97" max="97" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="98" max="98" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="99" max="99" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="100" max="100" width="23.5703125" customWidth="1"/>
-    <col min="101" max="101" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="106" max="106" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="108" max="108" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="90" max="90" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="91" max="91" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="23.54296875" customWidth="1"/>
+    <col min="101" max="101" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="106" max="106" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="107" max="107" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="108" max="108" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:108" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="16" t="s">
+    <row r="1" spans="1:108" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="B1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="C1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="D1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="E1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="F1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="G1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="H1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="I1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="J1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="K1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="L1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="M1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="N1" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="O1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="P1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="16" t="s">
+      <c r="Q1" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="R1" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="S1" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="17" t="s">
+      <c r="T1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="17" t="s">
+      <c r="U1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="16" t="s">
+      <c r="V1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="Y1" s="16" t="s">
+      <c r="W1" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="Z1" s="16" t="s">
+      <c r="X1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="Y1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="AB1" s="16" t="s">
+      <c r="Z1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AA1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AB1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="AE1" s="16" t="s">
+      <c r="AC1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AF1" s="9" t="s">
+      <c r="AD1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AE1" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="AH1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="AI1" s="10" t="s">
+      <c r="AG1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="AJ1" s="18" t="s">
+      <c r="AH1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AK1" s="18" t="s">
+      <c r="AI1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="AL1" s="16" t="s">
+      <c r="AJ1" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AK1" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="AN1" s="16" t="s">
+      <c r="AL1" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="AO1" s="9" t="s">
+      <c r="AM1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="AP1" s="9" t="s">
+      <c r="AN1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="AQ1" s="9" t="s">
+      <c r="AO1" s="11" t="s">
         <v>45</v>
       </c>
+      <c r="AP1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="AQ1" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="AR1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AS1" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="AS1" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="AT1" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AU1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AV1" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="AW1" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="AX1" s="9" t="s">
+      <c r="AV1" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="AY1" s="10" t="s">
+      <c r="AW1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="AZ1" s="16" t="s">
+      <c r="AX1" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="BA1" s="10" t="s">
+      <c r="AY1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="BB1" s="10" t="s">
+      <c r="AZ1" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="BC1" s="9" t="s">
+      <c r="BA1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="BD1" s="16" t="s">
+      <c r="BB1" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="BE1" s="16" t="s">
+      <c r="BC1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="BF1" s="16" t="s">
+      <c r="BD1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="BG1" s="19" t="s">
+      <c r="BE1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="BH1" s="10" t="s">
+      <c r="BF1" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="BI1" s="9" t="s">
+      <c r="BG1" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="BJ1" s="16" t="s">
+      <c r="BH1" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="BK1" s="16" t="s">
+      <c r="BI1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="BL1" s="16" t="s">
+      <c r="BJ1" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="BM1" s="16" t="s">
+      <c r="BK1" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="BN1" s="9" t="s">
+      <c r="BL1" s="19" t="s">
         <v>68</v>
       </c>
+      <c r="BM1" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="BN1" s="11" t="s">
+        <v>70</v>
+      </c>
       <c r="BO1" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="BP1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="BQ1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="BQ1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="BR1" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="BS1" s="9" t="s">
+      <c r="BR1" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="BS1" s="11" t="s">
         <v>1</v>
       </c>
       <c r="BT1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="BU1" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="BU1" s="11" t="s">
+        <v>75</v>
       </c>
       <c r="BV1" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="BW1" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="BX1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="BY1" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="BY1" s="25" t="s">
+        <v>79</v>
       </c>
       <c r="BZ1" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="CA1" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="CC1" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="CD1" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="CE1" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="CF1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="CG1" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="CH1" s="9" t="s">
         <v>86</v>
       </c>
+      <c r="CG1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="CH1" s="11" t="s">
+        <v>88</v>
+      </c>
       <c r="CI1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="CJ1" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="CK1" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="CL1" s="9" t="s">
+      <c r="CJ1" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="CM1" s="9" t="s">
+      <c r="CK1" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="CN1" s="9" t="s">
+      <c r="CL1" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="CO1" s="9" t="s">
+      <c r="CM1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="CP1" s="16" t="s">
+      <c r="CN1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="CQ1" s="10" t="s">
+      <c r="CO1" s="11" t="s">
         <v>95</v>
       </c>
+      <c r="CP1" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="CQ1" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="CR1" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="CS1" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="CT1" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="CU1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="CV1" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="CV1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="CW1" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="CX1" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="CY1" s="9" t="s">
+      <c r="CW1" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="CZ1" s="9" t="s">
+      <c r="CX1" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="DA1" s="9" t="s">
+      <c r="CY1" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="DB1" s="16" t="s">
+      <c r="CZ1" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="DC1" s="16" t="s">
+      <c r="DA1" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="DD1" s="16" t="s">
+      <c r="DB1" s="19" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="2" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC1" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="DD1" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1315,11 +2123,11 @@
       <c r="H2" s="5"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
-      <c r="K2" s="15"/>
+      <c r="K2" s="18"/>
       <c r="L2" s="7"/>
       <c r="M2" s="4"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="21"/>
+      <c r="O2" s="26"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
@@ -1357,23 +2165,23 @@
       <c r="AY2" s="4"/>
       <c r="AZ2" s="3"/>
       <c r="BA2" s="4"/>
-      <c r="BB2" s="22"/>
+      <c r="BB2" s="27"/>
       <c r="BC2" s="3"/>
       <c r="BD2" s="3"/>
       <c r="BE2" s="3"/>
       <c r="BF2" s="3"/>
-      <c r="BG2" s="13"/>
+      <c r="BG2" s="15"/>
       <c r="BH2" s="4"/>
       <c r="BI2" s="3"/>
       <c r="BJ2" s="3"/>
-      <c r="BL2" s="12"/>
-      <c r="BM2" s="12"/>
-      <c r="BN2" s="13"/>
+      <c r="BL2" s="14"/>
+      <c r="BM2" s="14"/>
+      <c r="BN2" s="15"/>
       <c r="BO2" s="3"/>
       <c r="BP2" s="3"/>
-      <c r="BQ2" s="13"/>
+      <c r="BQ2" s="15"/>
       <c r="BR2" s="6"/>
-      <c r="BS2" s="14"/>
+      <c r="BS2" s="17"/>
       <c r="BT2" s="3"/>
       <c r="BU2" s="3"/>
       <c r="BV2" s="3"/>
@@ -1382,12 +2190,12 @@
       <c r="BY2" s="3"/>
       <c r="BZ2" s="3"/>
       <c r="CA2" s="3"/>
-      <c r="CB2" s="13"/>
+      <c r="CB2" s="15"/>
       <c r="CC2" s="3"/>
       <c r="CD2" s="3"/>
       <c r="CE2" s="3"/>
       <c r="CF2" s="3"/>
-      <c r="CG2" s="23"/>
+      <c r="CG2" s="28"/>
       <c r="CH2" s="3"/>
       <c r="CI2" s="3"/>
       <c r="CJ2" s="6"/>
@@ -1398,7 +2206,7 @@
       <c r="CO2" s="6"/>
       <c r="CP2" s="3"/>
       <c r="CQ2" s="4"/>
-      <c r="CR2" s="13"/>
+      <c r="CR2" s="15"/>
       <c r="CS2" s="3"/>
       <c r="CT2" s="3"/>
       <c r="CU2" s="3"/>
@@ -1409,10 +2217,10 @@
       <c r="CZ2" s="8"/>
       <c r="DA2" s="3"/>
       <c r="DB2" s="3"/>
-      <c r="DC2" s="14"/>
-      <c r="DD2" s="14"/>
-    </row>
-    <row r="3" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC2" s="17"/>
+      <c r="DD2" s="17"/>
+    </row>
+    <row r="3" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1423,11 +2231,11 @@
       <c r="H3" s="5"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
-      <c r="K3" s="15"/>
+      <c r="K3" s="18"/>
       <c r="L3" s="7"/>
       <c r="M3" s="4"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="21"/>
+      <c r="O3" s="26"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
@@ -1465,23 +2273,23 @@
       <c r="AY3" s="4"/>
       <c r="AZ3" s="3"/>
       <c r="BA3" s="4"/>
-      <c r="BB3" s="22"/>
+      <c r="BB3" s="27"/>
       <c r="BC3" s="3"/>
       <c r="BD3" s="3"/>
       <c r="BE3" s="3"/>
       <c r="BF3" s="3"/>
-      <c r="BG3" s="13"/>
+      <c r="BG3" s="15"/>
       <c r="BH3" s="4"/>
       <c r="BI3" s="3"/>
       <c r="BJ3" s="3"/>
-      <c r="BL3" s="12"/>
-      <c r="BM3" s="12"/>
-      <c r="BN3" s="13"/>
+      <c r="BL3" s="14"/>
+      <c r="BM3" s="14"/>
+      <c r="BN3" s="15"/>
       <c r="BO3" s="3"/>
       <c r="BP3" s="3"/>
-      <c r="BQ3" s="13"/>
+      <c r="BQ3" s="15"/>
       <c r="BR3" s="6"/>
-      <c r="BS3" s="14"/>
+      <c r="BS3" s="17"/>
       <c r="BT3" s="3"/>
       <c r="BU3" s="3"/>
       <c r="BV3" s="3"/>
@@ -1490,12 +2298,12 @@
       <c r="BY3" s="3"/>
       <c r="BZ3" s="3"/>
       <c r="CA3" s="3"/>
-      <c r="CB3" s="13"/>
+      <c r="CB3" s="15"/>
       <c r="CC3" s="3"/>
       <c r="CD3" s="3"/>
       <c r="CE3" s="3"/>
       <c r="CF3" s="3"/>
-      <c r="CG3" s="23"/>
+      <c r="CG3" s="28"/>
       <c r="CH3" s="3"/>
       <c r="CI3" s="3"/>
       <c r="CJ3" s="6"/>
@@ -1506,7 +2314,7 @@
       <c r="CO3" s="6"/>
       <c r="CP3" s="3"/>
       <c r="CQ3" s="4"/>
-      <c r="CR3" s="13"/>
+      <c r="CR3" s="15"/>
       <c r="CS3" s="3"/>
       <c r="CT3" s="3"/>
       <c r="CU3" s="3"/>
@@ -1517,10 +2325,10 @@
       <c r="CZ3" s="8"/>
       <c r="DA3" s="3"/>
       <c r="DB3" s="3"/>
-      <c r="DC3" s="14"/>
-      <c r="DD3" s="14"/>
-    </row>
-    <row r="4" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC3" s="17"/>
+      <c r="DD3" s="17"/>
+    </row>
+    <row r="4" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -1531,11 +2339,11 @@
       <c r="H4" s="5"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="15"/>
+      <c r="K4" s="18"/>
       <c r="L4" s="7"/>
       <c r="M4" s="4"/>
       <c r="N4" s="6"/>
-      <c r="O4" s="21"/>
+      <c r="O4" s="26"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -1573,23 +2381,23 @@
       <c r="AY4" s="4"/>
       <c r="AZ4" s="3"/>
       <c r="BA4" s="4"/>
-      <c r="BB4" s="22"/>
+      <c r="BB4" s="27"/>
       <c r="BC4" s="3"/>
       <c r="BD4" s="3"/>
       <c r="BE4" s="3"/>
       <c r="BF4" s="3"/>
-      <c r="BG4" s="13"/>
+      <c r="BG4" s="15"/>
       <c r="BH4" s="4"/>
       <c r="BI4" s="3"/>
       <c r="BJ4" s="3"/>
-      <c r="BL4" s="12"/>
-      <c r="BM4" s="12"/>
-      <c r="BN4" s="13"/>
+      <c r="BL4" s="14"/>
+      <c r="BM4" s="14"/>
+      <c r="BN4" s="15"/>
       <c r="BO4" s="3"/>
       <c r="BP4" s="3"/>
-      <c r="BQ4" s="13"/>
+      <c r="BQ4" s="15"/>
       <c r="BR4" s="6"/>
-      <c r="BS4" s="14"/>
+      <c r="BS4" s="17"/>
       <c r="BT4" s="3"/>
       <c r="BU4" s="3"/>
       <c r="BV4" s="3"/>
@@ -1598,12 +2406,12 @@
       <c r="BY4" s="3"/>
       <c r="BZ4" s="3"/>
       <c r="CA4" s="3"/>
-      <c r="CB4" s="13"/>
+      <c r="CB4" s="15"/>
       <c r="CC4" s="3"/>
       <c r="CD4" s="3"/>
       <c r="CE4" s="3"/>
       <c r="CF4" s="3"/>
-      <c r="CG4" s="23"/>
+      <c r="CG4" s="28"/>
       <c r="CH4" s="3"/>
       <c r="CI4" s="3"/>
       <c r="CJ4" s="6"/>
@@ -1614,7 +2422,7 @@
       <c r="CO4" s="6"/>
       <c r="CP4" s="3"/>
       <c r="CQ4" s="4"/>
-      <c r="CR4" s="13"/>
+      <c r="CR4" s="15"/>
       <c r="CS4" s="3"/>
       <c r="CT4" s="3"/>
       <c r="CU4" s="3"/>
@@ -1625,10 +2433,10 @@
       <c r="CZ4" s="8"/>
       <c r="DA4" s="3"/>
       <c r="DB4" s="3"/>
-      <c r="DC4" s="14"/>
-      <c r="DD4" s="14"/>
-    </row>
-    <row r="5" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC4" s="17"/>
+      <c r="DD4" s="17"/>
+    </row>
+    <row r="5" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -1639,11 +2447,11 @@
       <c r="H5" s="5"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="15"/>
+      <c r="K5" s="18"/>
       <c r="L5" s="7"/>
       <c r="M5" s="4"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="21"/>
+      <c r="O5" s="26"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -1681,23 +2489,23 @@
       <c r="AY5" s="4"/>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="4"/>
-      <c r="BB5" s="22"/>
+      <c r="BB5" s="27"/>
       <c r="BC5" s="3"/>
       <c r="BD5" s="3"/>
       <c r="BE5" s="3"/>
       <c r="BF5" s="3"/>
-      <c r="BG5" s="13"/>
+      <c r="BG5" s="15"/>
       <c r="BH5" s="4"/>
       <c r="BI5" s="3"/>
       <c r="BJ5" s="3"/>
-      <c r="BL5" s="12"/>
-      <c r="BM5" s="12"/>
-      <c r="BN5" s="13"/>
+      <c r="BL5" s="14"/>
+      <c r="BM5" s="14"/>
+      <c r="BN5" s="15"/>
       <c r="BO5" s="3"/>
       <c r="BP5" s="3"/>
-      <c r="BQ5" s="13"/>
+      <c r="BQ5" s="15"/>
       <c r="BR5" s="6"/>
-      <c r="BS5" s="14"/>
+      <c r="BS5" s="17"/>
       <c r="BT5" s="3"/>
       <c r="BU5" s="3"/>
       <c r="BV5" s="3"/>
@@ -1706,12 +2514,12 @@
       <c r="BY5" s="3"/>
       <c r="BZ5" s="3"/>
       <c r="CA5" s="3"/>
-      <c r="CB5" s="13"/>
+      <c r="CB5" s="15"/>
       <c r="CC5" s="3"/>
       <c r="CD5" s="3"/>
       <c r="CE5" s="3"/>
       <c r="CF5" s="3"/>
-      <c r="CG5" s="23"/>
+      <c r="CG5" s="28"/>
       <c r="CH5" s="3"/>
       <c r="CI5" s="3"/>
       <c r="CJ5" s="6"/>
@@ -1722,7 +2530,7 @@
       <c r="CO5" s="6"/>
       <c r="CP5" s="3"/>
       <c r="CQ5" s="4"/>
-      <c r="CR5" s="13"/>
+      <c r="CR5" s="15"/>
       <c r="CS5" s="3"/>
       <c r="CT5" s="3"/>
       <c r="CU5" s="3"/>
@@ -1733,10 +2541,10 @@
       <c r="CZ5" s="8"/>
       <c r="DA5" s="3"/>
       <c r="DB5" s="3"/>
-      <c r="DC5" s="14"/>
-      <c r="DD5" s="14"/>
-    </row>
-    <row r="6" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC5" s="17"/>
+      <c r="DD5" s="17"/>
+    </row>
+    <row r="6" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1747,11 +2555,11 @@
       <c r="H6" s="5"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="15"/>
+      <c r="K6" s="18"/>
       <c r="L6" s="7"/>
       <c r="M6" s="4"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="21"/>
+      <c r="O6" s="26"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -1789,23 +2597,23 @@
       <c r="AY6" s="4"/>
       <c r="AZ6" s="3"/>
       <c r="BA6" s="4"/>
-      <c r="BB6" s="22"/>
+      <c r="BB6" s="27"/>
       <c r="BC6" s="3"/>
       <c r="BD6" s="3"/>
       <c r="BE6" s="3"/>
       <c r="BF6" s="3"/>
-      <c r="BG6" s="13"/>
+      <c r="BG6" s="15"/>
       <c r="BH6" s="4"/>
       <c r="BI6" s="3"/>
       <c r="BJ6" s="3"/>
-      <c r="BL6" s="12"/>
-      <c r="BM6" s="12"/>
-      <c r="BN6" s="13"/>
+      <c r="BL6" s="14"/>
+      <c r="BM6" s="14"/>
+      <c r="BN6" s="15"/>
       <c r="BO6" s="3"/>
       <c r="BP6" s="3"/>
-      <c r="BQ6" s="13"/>
+      <c r="BQ6" s="15"/>
       <c r="BR6" s="6"/>
-      <c r="BS6" s="14"/>
+      <c r="BS6" s="17"/>
       <c r="BT6" s="3"/>
       <c r="BU6" s="3"/>
       <c r="BV6" s="3"/>
@@ -1814,12 +2622,12 @@
       <c r="BY6" s="3"/>
       <c r="BZ6" s="3"/>
       <c r="CA6" s="3"/>
-      <c r="CB6" s="13"/>
+      <c r="CB6" s="15"/>
       <c r="CC6" s="3"/>
       <c r="CD6" s="3"/>
       <c r="CE6" s="3"/>
       <c r="CF6" s="3"/>
-      <c r="CG6" s="23"/>
+      <c r="CG6" s="28"/>
       <c r="CH6" s="3"/>
       <c r="CI6" s="3"/>
       <c r="CJ6" s="6"/>
@@ -1830,7 +2638,7 @@
       <c r="CO6" s="6"/>
       <c r="CP6" s="3"/>
       <c r="CQ6" s="4"/>
-      <c r="CR6" s="13"/>
+      <c r="CR6" s="15"/>
       <c r="CS6" s="3"/>
       <c r="CT6" s="3"/>
       <c r="CU6" s="3"/>
@@ -1841,10 +2649,10 @@
       <c r="CZ6" s="8"/>
       <c r="DA6" s="3"/>
       <c r="DB6" s="3"/>
-      <c r="DC6" s="14"/>
-      <c r="DD6" s="14"/>
-    </row>
-    <row r="7" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC6" s="17"/>
+      <c r="DD6" s="17"/>
+    </row>
+    <row r="7" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1855,11 +2663,11 @@
       <c r="H7" s="5"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-      <c r="K7" s="15"/>
+      <c r="K7" s="18"/>
       <c r="L7" s="7"/>
       <c r="M7" s="4"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="21"/>
+      <c r="O7" s="26"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -1897,23 +2705,23 @@
       <c r="AY7" s="4"/>
       <c r="AZ7" s="3"/>
       <c r="BA7" s="4"/>
-      <c r="BB7" s="22"/>
+      <c r="BB7" s="27"/>
       <c r="BC7" s="3"/>
       <c r="BD7" s="3"/>
       <c r="BE7" s="3"/>
       <c r="BF7" s="3"/>
-      <c r="BG7" s="13"/>
+      <c r="BG7" s="15"/>
       <c r="BH7" s="4"/>
       <c r="BI7" s="3"/>
       <c r="BJ7" s="3"/>
-      <c r="BL7" s="12"/>
-      <c r="BM7" s="12"/>
-      <c r="BN7" s="13"/>
+      <c r="BL7" s="14"/>
+      <c r="BM7" s="14"/>
+      <c r="BN7" s="15"/>
       <c r="BO7" s="3"/>
       <c r="BP7" s="3"/>
-      <c r="BQ7" s="13"/>
+      <c r="BQ7" s="15"/>
       <c r="BR7" s="6"/>
-      <c r="BS7" s="14"/>
+      <c r="BS7" s="17"/>
       <c r="BT7" s="3"/>
       <c r="BU7" s="3"/>
       <c r="BV7" s="3"/>
@@ -1922,12 +2730,12 @@
       <c r="BY7" s="3"/>
       <c r="BZ7" s="3"/>
       <c r="CA7" s="3"/>
-      <c r="CB7" s="13"/>
+      <c r="CB7" s="15"/>
       <c r="CC7" s="3"/>
       <c r="CD7" s="3"/>
       <c r="CE7" s="3"/>
       <c r="CF7" s="3"/>
-      <c r="CG7" s="23"/>
+      <c r="CG7" s="28"/>
       <c r="CH7" s="3"/>
       <c r="CI7" s="3"/>
       <c r="CJ7" s="6"/>
@@ -1938,7 +2746,7 @@
       <c r="CO7" s="6"/>
       <c r="CP7" s="3"/>
       <c r="CQ7" s="4"/>
-      <c r="CR7" s="13"/>
+      <c r="CR7" s="15"/>
       <c r="CS7" s="3"/>
       <c r="CT7" s="3"/>
       <c r="CU7" s="3"/>
@@ -1949,10 +2757,10 @@
       <c r="CZ7" s="8"/>
       <c r="DA7" s="3"/>
       <c r="DB7" s="3"/>
-      <c r="DC7" s="14"/>
-      <c r="DD7" s="14"/>
-    </row>
-    <row r="8" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC7" s="17"/>
+      <c r="DD7" s="17"/>
+    </row>
+    <row r="8" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1963,11 +2771,11 @@
       <c r="H8" s="5"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
-      <c r="K8" s="15"/>
+      <c r="K8" s="18"/>
       <c r="L8" s="7"/>
       <c r="M8" s="4"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="21"/>
+      <c r="O8" s="26"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -2005,23 +2813,23 @@
       <c r="AY8" s="4"/>
       <c r="AZ8" s="3"/>
       <c r="BA8" s="4"/>
-      <c r="BB8" s="22"/>
+      <c r="BB8" s="27"/>
       <c r="BC8" s="3"/>
       <c r="BD8" s="3"/>
       <c r="BE8" s="3"/>
       <c r="BF8" s="3"/>
-      <c r="BG8" s="13"/>
+      <c r="BG8" s="15"/>
       <c r="BH8" s="4"/>
       <c r="BI8" s="3"/>
       <c r="BJ8" s="3"/>
-      <c r="BL8" s="12"/>
-      <c r="BM8" s="12"/>
-      <c r="BN8" s="13"/>
+      <c r="BL8" s="14"/>
+      <c r="BM8" s="14"/>
+      <c r="BN8" s="15"/>
       <c r="BO8" s="3"/>
       <c r="BP8" s="3"/>
-      <c r="BQ8" s="13"/>
+      <c r="BQ8" s="15"/>
       <c r="BR8" s="6"/>
-      <c r="BS8" s="14"/>
+      <c r="BS8" s="17"/>
       <c r="BT8" s="3"/>
       <c r="BU8" s="3"/>
       <c r="BV8" s="3"/>
@@ -2030,12 +2838,12 @@
       <c r="BY8" s="3"/>
       <c r="BZ8" s="3"/>
       <c r="CA8" s="3"/>
-      <c r="CB8" s="13"/>
+      <c r="CB8" s="15"/>
       <c r="CC8" s="3"/>
       <c r="CD8" s="3"/>
       <c r="CE8" s="3"/>
       <c r="CF8" s="3"/>
-      <c r="CG8" s="23"/>
+      <c r="CG8" s="28"/>
       <c r="CH8" s="3"/>
       <c r="CI8" s="3"/>
       <c r="CJ8" s="6"/>
@@ -2046,7 +2854,7 @@
       <c r="CO8" s="6"/>
       <c r="CP8" s="3"/>
       <c r="CQ8" s="4"/>
-      <c r="CR8" s="13"/>
+      <c r="CR8" s="15"/>
       <c r="CS8" s="3"/>
       <c r="CT8" s="3"/>
       <c r="CU8" s="3"/>
@@ -2057,10 +2865,10 @@
       <c r="CZ8" s="8"/>
       <c r="DA8" s="3"/>
       <c r="DB8" s="3"/>
-      <c r="DC8" s="14"/>
-      <c r="DD8" s="14"/>
-    </row>
-    <row r="9" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC8" s="17"/>
+      <c r="DD8" s="17"/>
+    </row>
+    <row r="9" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2071,11 +2879,11 @@
       <c r="H9" s="5"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="15"/>
+      <c r="K9" s="18"/>
       <c r="L9" s="7"/>
       <c r="M9" s="4"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="21"/>
+      <c r="O9" s="26"/>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -2113,23 +2921,23 @@
       <c r="AY9" s="4"/>
       <c r="AZ9" s="3"/>
       <c r="BA9" s="4"/>
-      <c r="BB9" s="22"/>
+      <c r="BB9" s="27"/>
       <c r="BC9" s="3"/>
       <c r="BD9" s="3"/>
       <c r="BE9" s="3"/>
       <c r="BF9" s="3"/>
-      <c r="BG9" s="13"/>
+      <c r="BG9" s="15"/>
       <c r="BH9" s="4"/>
       <c r="BI9" s="3"/>
       <c r="BJ9" s="3"/>
-      <c r="BL9" s="12"/>
-      <c r="BM9" s="12"/>
-      <c r="BN9" s="13"/>
+      <c r="BL9" s="14"/>
+      <c r="BM9" s="14"/>
+      <c r="BN9" s="15"/>
       <c r="BO9" s="3"/>
       <c r="BP9" s="3"/>
-      <c r="BQ9" s="13"/>
+      <c r="BQ9" s="15"/>
       <c r="BR9" s="6"/>
-      <c r="BS9" s="14"/>
+      <c r="BS9" s="17"/>
       <c r="BT9" s="3"/>
       <c r="BU9" s="3"/>
       <c r="BV9" s="3"/>
@@ -2138,12 +2946,12 @@
       <c r="BY9" s="3"/>
       <c r="BZ9" s="3"/>
       <c r="CA9" s="3"/>
-      <c r="CB9" s="13"/>
+      <c r="CB9" s="15"/>
       <c r="CC9" s="3"/>
       <c r="CD9" s="3"/>
       <c r="CE9" s="3"/>
       <c r="CF9" s="3"/>
-      <c r="CG9" s="23"/>
+      <c r="CG9" s="28"/>
       <c r="CH9" s="3"/>
       <c r="CI9" s="3"/>
       <c r="CJ9" s="6"/>
@@ -2154,7 +2962,7 @@
       <c r="CO9" s="6"/>
       <c r="CP9" s="3"/>
       <c r="CQ9" s="4"/>
-      <c r="CR9" s="13"/>
+      <c r="CR9" s="15"/>
       <c r="CS9" s="3"/>
       <c r="CT9" s="3"/>
       <c r="CU9" s="3"/>
@@ -2165,10 +2973,10 @@
       <c r="CZ9" s="8"/>
       <c r="DA9" s="3"/>
       <c r="DB9" s="3"/>
-      <c r="DC9" s="14"/>
-      <c r="DD9" s="14"/>
-    </row>
-    <row r="10" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC9" s="17"/>
+      <c r="DD9" s="17"/>
+    </row>
+    <row r="10" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2179,11 +2987,11 @@
       <c r="H10" s="5"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="15"/>
+      <c r="K10" s="18"/>
       <c r="L10" s="7"/>
       <c r="M10" s="4"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="21"/>
+      <c r="O10" s="26"/>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -2221,23 +3029,23 @@
       <c r="AY10" s="4"/>
       <c r="AZ10" s="3"/>
       <c r="BA10" s="4"/>
-      <c r="BB10" s="22"/>
+      <c r="BB10" s="27"/>
       <c r="BC10" s="3"/>
       <c r="BD10" s="3"/>
       <c r="BE10" s="3"/>
       <c r="BF10" s="3"/>
-      <c r="BG10" s="13"/>
+      <c r="BG10" s="15"/>
       <c r="BH10" s="4"/>
       <c r="BI10" s="3"/>
       <c r="BJ10" s="3"/>
-      <c r="BL10" s="12"/>
-      <c r="BM10" s="12"/>
-      <c r="BN10" s="13"/>
+      <c r="BL10" s="14"/>
+      <c r="BM10" s="14"/>
+      <c r="BN10" s="15"/>
       <c r="BO10" s="3"/>
       <c r="BP10" s="3"/>
-      <c r="BQ10" s="13"/>
+      <c r="BQ10" s="15"/>
       <c r="BR10" s="6"/>
-      <c r="BS10" s="14"/>
+      <c r="BS10" s="17"/>
       <c r="BT10" s="3"/>
       <c r="BU10" s="3"/>
       <c r="BV10" s="3"/>
@@ -2246,12 +3054,12 @@
       <c r="BY10" s="3"/>
       <c r="BZ10" s="3"/>
       <c r="CA10" s="3"/>
-      <c r="CB10" s="13"/>
+      <c r="CB10" s="15"/>
       <c r="CC10" s="3"/>
       <c r="CD10" s="3"/>
       <c r="CE10" s="3"/>
       <c r="CF10" s="3"/>
-      <c r="CG10" s="23"/>
+      <c r="CG10" s="28"/>
       <c r="CH10" s="3"/>
       <c r="CI10" s="3"/>
       <c r="CJ10" s="6"/>
@@ -2262,7 +3070,7 @@
       <c r="CO10" s="6"/>
       <c r="CP10" s="3"/>
       <c r="CQ10" s="4"/>
-      <c r="CR10" s="13"/>
+      <c r="CR10" s="15"/>
       <c r="CS10" s="3"/>
       <c r="CT10" s="3"/>
       <c r="CU10" s="3"/>
@@ -2273,10 +3081,10 @@
       <c r="CZ10" s="8"/>
       <c r="DA10" s="3"/>
       <c r="DB10" s="3"/>
-      <c r="DC10" s="14"/>
-      <c r="DD10" s="14"/>
-    </row>
-    <row r="11" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC10" s="17"/>
+      <c r="DD10" s="17"/>
+    </row>
+    <row r="11" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -2287,11 +3095,11 @@
       <c r="H11" s="5"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="15"/>
+      <c r="K11" s="18"/>
       <c r="L11" s="7"/>
       <c r="M11" s="4"/>
       <c r="N11" s="6"/>
-      <c r="O11" s="21"/>
+      <c r="O11" s="26"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -2329,23 +3137,23 @@
       <c r="AY11" s="4"/>
       <c r="AZ11" s="3"/>
       <c r="BA11" s="4"/>
-      <c r="BB11" s="22"/>
+      <c r="BB11" s="27"/>
       <c r="BC11" s="3"/>
       <c r="BD11" s="3"/>
       <c r="BE11" s="3"/>
       <c r="BF11" s="3"/>
-      <c r="BG11" s="13"/>
+      <c r="BG11" s="15"/>
       <c r="BH11" s="4"/>
       <c r="BI11" s="3"/>
       <c r="BJ11" s="3"/>
-      <c r="BL11" s="12"/>
-      <c r="BM11" s="12"/>
-      <c r="BN11" s="13"/>
+      <c r="BL11" s="14"/>
+      <c r="BM11" s="14"/>
+      <c r="BN11" s="15"/>
       <c r="BO11" s="3"/>
       <c r="BP11" s="3"/>
-      <c r="BQ11" s="13"/>
+      <c r="BQ11" s="15"/>
       <c r="BR11" s="6"/>
-      <c r="BS11" s="14"/>
+      <c r="BS11" s="17"/>
       <c r="BT11" s="3"/>
       <c r="BU11" s="3"/>
       <c r="BV11" s="3"/>
@@ -2354,12 +3162,12 @@
       <c r="BY11" s="3"/>
       <c r="BZ11" s="3"/>
       <c r="CA11" s="3"/>
-      <c r="CB11" s="13"/>
+      <c r="CB11" s="15"/>
       <c r="CC11" s="3"/>
       <c r="CD11" s="3"/>
       <c r="CE11" s="3"/>
       <c r="CF11" s="3"/>
-      <c r="CG11" s="23"/>
+      <c r="CG11" s="28"/>
       <c r="CH11" s="3"/>
       <c r="CI11" s="3"/>
       <c r="CJ11" s="6"/>
@@ -2370,7 +3178,7 @@
       <c r="CO11" s="6"/>
       <c r="CP11" s="3"/>
       <c r="CQ11" s="4"/>
-      <c r="CR11" s="13"/>
+      <c r="CR11" s="15"/>
       <c r="CS11" s="3"/>
       <c r="CT11" s="3"/>
       <c r="CU11" s="3"/>
@@ -2381,10 +3189,10 @@
       <c r="CZ11" s="8"/>
       <c r="DA11" s="3"/>
       <c r="DB11" s="3"/>
-      <c r="DC11" s="14"/>
-      <c r="DD11" s="14"/>
-    </row>
-    <row r="12" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC11" s="17"/>
+      <c r="DD11" s="17"/>
+    </row>
+    <row r="12" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2395,11 +3203,11 @@
       <c r="H12" s="5"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="15"/>
+      <c r="K12" s="18"/>
       <c r="L12" s="7"/>
       <c r="M12" s="4"/>
       <c r="N12" s="6"/>
-      <c r="O12" s="21"/>
+      <c r="O12" s="26"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -2437,23 +3245,23 @@
       <c r="AY12" s="4"/>
       <c r="AZ12" s="3"/>
       <c r="BA12" s="4"/>
-      <c r="BB12" s="22"/>
+      <c r="BB12" s="27"/>
       <c r="BC12" s="3"/>
       <c r="BD12" s="3"/>
       <c r="BE12" s="3"/>
       <c r="BF12" s="3"/>
-      <c r="BG12" s="13"/>
+      <c r="BG12" s="15"/>
       <c r="BH12" s="4"/>
       <c r="BI12" s="3"/>
       <c r="BJ12" s="3"/>
-      <c r="BL12" s="12"/>
-      <c r="BM12" s="12"/>
-      <c r="BN12" s="13"/>
+      <c r="BL12" s="14"/>
+      <c r="BM12" s="14"/>
+      <c r="BN12" s="15"/>
       <c r="BO12" s="3"/>
       <c r="BP12" s="3"/>
-      <c r="BQ12" s="13"/>
+      <c r="BQ12" s="15"/>
       <c r="BR12" s="6"/>
-      <c r="BS12" s="14"/>
+      <c r="BS12" s="17"/>
       <c r="BT12" s="3"/>
       <c r="BU12" s="3"/>
       <c r="BV12" s="3"/>
@@ -2462,12 +3270,12 @@
       <c r="BY12" s="3"/>
       <c r="BZ12" s="3"/>
       <c r="CA12" s="3"/>
-      <c r="CB12" s="13"/>
+      <c r="CB12" s="15"/>
       <c r="CC12" s="3"/>
       <c r="CD12" s="3"/>
       <c r="CE12" s="3"/>
       <c r="CF12" s="3"/>
-      <c r="CG12" s="23"/>
+      <c r="CG12" s="28"/>
       <c r="CH12" s="3"/>
       <c r="CI12" s="3"/>
       <c r="CJ12" s="6"/>
@@ -2478,7 +3286,7 @@
       <c r="CO12" s="6"/>
       <c r="CP12" s="3"/>
       <c r="CQ12" s="4"/>
-      <c r="CR12" s="13"/>
+      <c r="CR12" s="15"/>
       <c r="CS12" s="3"/>
       <c r="CT12" s="3"/>
       <c r="CU12" s="3"/>
@@ -2489,10 +3297,10 @@
       <c r="CZ12" s="8"/>
       <c r="DA12" s="3"/>
       <c r="DB12" s="3"/>
-      <c r="DC12" s="14"/>
-      <c r="DD12" s="14"/>
-    </row>
-    <row r="13" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC12" s="17"/>
+      <c r="DD12" s="17"/>
+    </row>
+    <row r="13" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2503,11 +3311,11 @@
       <c r="H13" s="5"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="15"/>
+      <c r="K13" s="18"/>
       <c r="L13" s="7"/>
       <c r="M13" s="4"/>
       <c r="N13" s="6"/>
-      <c r="O13" s="21"/>
+      <c r="O13" s="26"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
@@ -2545,23 +3353,23 @@
       <c r="AY13" s="4"/>
       <c r="AZ13" s="3"/>
       <c r="BA13" s="4"/>
-      <c r="BB13" s="22"/>
+      <c r="BB13" s="27"/>
       <c r="BC13" s="3"/>
       <c r="BD13" s="3"/>
       <c r="BE13" s="3"/>
       <c r="BF13" s="3"/>
-      <c r="BG13" s="13"/>
+      <c r="BG13" s="15"/>
       <c r="BH13" s="4"/>
       <c r="BI13" s="3"/>
       <c r="BJ13" s="3"/>
-      <c r="BL13" s="12"/>
-      <c r="BM13" s="12"/>
-      <c r="BN13" s="13"/>
+      <c r="BL13" s="14"/>
+      <c r="BM13" s="14"/>
+      <c r="BN13" s="15"/>
       <c r="BO13" s="3"/>
       <c r="BP13" s="3"/>
-      <c r="BQ13" s="13"/>
+      <c r="BQ13" s="15"/>
       <c r="BR13" s="6"/>
-      <c r="BS13" s="14"/>
+      <c r="BS13" s="17"/>
       <c r="BT13" s="3"/>
       <c r="BU13" s="3"/>
       <c r="BV13" s="3"/>
@@ -2570,12 +3378,12 @@
       <c r="BY13" s="3"/>
       <c r="BZ13" s="3"/>
       <c r="CA13" s="3"/>
-      <c r="CB13" s="13"/>
+      <c r="CB13" s="15"/>
       <c r="CC13" s="3"/>
       <c r="CD13" s="3"/>
       <c r="CE13" s="3"/>
       <c r="CF13" s="3"/>
-      <c r="CG13" s="23"/>
+      <c r="CG13" s="28"/>
       <c r="CH13" s="3"/>
       <c r="CI13" s="3"/>
       <c r="CJ13" s="6"/>
@@ -2586,7 +3394,7 @@
       <c r="CO13" s="6"/>
       <c r="CP13" s="3"/>
       <c r="CQ13" s="4"/>
-      <c r="CR13" s="13"/>
+      <c r="CR13" s="15"/>
       <c r="CS13" s="3"/>
       <c r="CT13" s="3"/>
       <c r="CU13" s="3"/>
@@ -2597,10 +3405,10 @@
       <c r="CZ13" s="8"/>
       <c r="DA13" s="3"/>
       <c r="DB13" s="3"/>
-      <c r="DC13" s="14"/>
-      <c r="DD13" s="14"/>
-    </row>
-    <row r="14" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC13" s="17"/>
+      <c r="DD13" s="17"/>
+    </row>
+    <row r="14" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -2611,11 +3419,11 @@
       <c r="H14" s="5"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
-      <c r="K14" s="15"/>
+      <c r="K14" s="18"/>
       <c r="L14" s="7"/>
       <c r="M14" s="4"/>
       <c r="N14" s="6"/>
-      <c r="O14" s="21"/>
+      <c r="O14" s="26"/>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -2653,23 +3461,23 @@
       <c r="AY14" s="4"/>
       <c r="AZ14" s="3"/>
       <c r="BA14" s="4"/>
-      <c r="BB14" s="22"/>
+      <c r="BB14" s="27"/>
       <c r="BC14" s="3"/>
       <c r="BD14" s="3"/>
       <c r="BE14" s="3"/>
       <c r="BF14" s="3"/>
-      <c r="BG14" s="13"/>
+      <c r="BG14" s="15"/>
       <c r="BH14" s="4"/>
       <c r="BI14" s="3"/>
       <c r="BJ14" s="3"/>
-      <c r="BL14" s="12"/>
-      <c r="BM14" s="12"/>
-      <c r="BN14" s="13"/>
+      <c r="BL14" s="14"/>
+      <c r="BM14" s="14"/>
+      <c r="BN14" s="15"/>
       <c r="BO14" s="3"/>
       <c r="BP14" s="3"/>
-      <c r="BQ14" s="13"/>
+      <c r="BQ14" s="15"/>
       <c r="BR14" s="6"/>
-      <c r="BS14" s="14"/>
+      <c r="BS14" s="17"/>
       <c r="BT14" s="3"/>
       <c r="BU14" s="3"/>
       <c r="BV14" s="3"/>
@@ -2678,12 +3486,12 @@
       <c r="BY14" s="3"/>
       <c r="BZ14" s="3"/>
       <c r="CA14" s="3"/>
-      <c r="CB14" s="13"/>
+      <c r="CB14" s="15"/>
       <c r="CC14" s="3"/>
       <c r="CD14" s="3"/>
       <c r="CE14" s="3"/>
       <c r="CF14" s="3"/>
-      <c r="CG14" s="23"/>
+      <c r="CG14" s="28"/>
       <c r="CH14" s="3"/>
       <c r="CI14" s="3"/>
       <c r="CJ14" s="6"/>
@@ -2694,7 +3502,7 @@
       <c r="CO14" s="6"/>
       <c r="CP14" s="3"/>
       <c r="CQ14" s="4"/>
-      <c r="CR14" s="13"/>
+      <c r="CR14" s="15"/>
       <c r="CS14" s="3"/>
       <c r="CT14" s="3"/>
       <c r="CU14" s="3"/>
@@ -2705,10 +3513,10 @@
       <c r="CZ14" s="8"/>
       <c r="DA14" s="3"/>
       <c r="DB14" s="3"/>
-      <c r="DC14" s="14"/>
-      <c r="DD14" s="14"/>
-    </row>
-    <row r="15" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC14" s="17"/>
+      <c r="DD14" s="17"/>
+    </row>
+    <row r="15" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -2719,11 +3527,11 @@
       <c r="H15" s="5"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="K15" s="15"/>
+      <c r="K15" s="18"/>
       <c r="L15" s="7"/>
       <c r="M15" s="4"/>
       <c r="N15" s="6"/>
-      <c r="O15" s="21"/>
+      <c r="O15" s="26"/>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -2761,23 +3569,23 @@
       <c r="AY15" s="4"/>
       <c r="AZ15" s="3"/>
       <c r="BA15" s="4"/>
-      <c r="BB15" s="22"/>
+      <c r="BB15" s="27"/>
       <c r="BC15" s="3"/>
       <c r="BD15" s="3"/>
       <c r="BE15" s="3"/>
       <c r="BF15" s="3"/>
-      <c r="BG15" s="13"/>
+      <c r="BG15" s="15"/>
       <c r="BH15" s="4"/>
       <c r="BI15" s="3"/>
       <c r="BJ15" s="3"/>
-      <c r="BL15" s="12"/>
-      <c r="BM15" s="12"/>
-      <c r="BN15" s="13"/>
+      <c r="BL15" s="14"/>
+      <c r="BM15" s="14"/>
+      <c r="BN15" s="15"/>
       <c r="BO15" s="3"/>
       <c r="BP15" s="3"/>
-      <c r="BQ15" s="13"/>
+      <c r="BQ15" s="15"/>
       <c r="BR15" s="6"/>
-      <c r="BS15" s="14"/>
+      <c r="BS15" s="17"/>
       <c r="BT15" s="3"/>
       <c r="BU15" s="3"/>
       <c r="BV15" s="3"/>
@@ -2786,12 +3594,12 @@
       <c r="BY15" s="3"/>
       <c r="BZ15" s="3"/>
       <c r="CA15" s="3"/>
-      <c r="CB15" s="13"/>
+      <c r="CB15" s="15"/>
       <c r="CC15" s="3"/>
       <c r="CD15" s="3"/>
       <c r="CE15" s="3"/>
       <c r="CF15" s="3"/>
-      <c r="CG15" s="23"/>
+      <c r="CG15" s="28"/>
       <c r="CH15" s="3"/>
       <c r="CI15" s="3"/>
       <c r="CJ15" s="6"/>
@@ -2802,7 +3610,7 @@
       <c r="CO15" s="6"/>
       <c r="CP15" s="3"/>
       <c r="CQ15" s="4"/>
-      <c r="CR15" s="13"/>
+      <c r="CR15" s="15"/>
       <c r="CS15" s="3"/>
       <c r="CT15" s="3"/>
       <c r="CU15" s="3"/>
@@ -2813,10 +3621,10 @@
       <c r="CZ15" s="8"/>
       <c r="DA15" s="3"/>
       <c r="DB15" s="3"/>
-      <c r="DC15" s="14"/>
-      <c r="DD15" s="14"/>
-    </row>
-    <row r="16" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC15" s="17"/>
+      <c r="DD15" s="17"/>
+    </row>
+    <row r="16" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2827,11 +3635,11 @@
       <c r="H16" s="5"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="K16" s="15"/>
+      <c r="K16" s="18"/>
       <c r="L16" s="7"/>
       <c r="M16" s="4"/>
       <c r="N16" s="6"/>
-      <c r="O16" s="21"/>
+      <c r="O16" s="26"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -2869,23 +3677,23 @@
       <c r="AY16" s="4"/>
       <c r="AZ16" s="3"/>
       <c r="BA16" s="4"/>
-      <c r="BB16" s="22"/>
+      <c r="BB16" s="27"/>
       <c r="BC16" s="3"/>
       <c r="BD16" s="3"/>
       <c r="BE16" s="3"/>
       <c r="BF16" s="3"/>
-      <c r="BG16" s="13"/>
+      <c r="BG16" s="15"/>
       <c r="BH16" s="4"/>
       <c r="BI16" s="3"/>
       <c r="BJ16" s="3"/>
-      <c r="BL16" s="12"/>
-      <c r="BM16" s="12"/>
-      <c r="BN16" s="13"/>
+      <c r="BL16" s="14"/>
+      <c r="BM16" s="14"/>
+      <c r="BN16" s="15"/>
       <c r="BO16" s="3"/>
       <c r="BP16" s="3"/>
-      <c r="BQ16" s="13"/>
+      <c r="BQ16" s="15"/>
       <c r="BR16" s="6"/>
-      <c r="BS16" s="14"/>
+      <c r="BS16" s="17"/>
       <c r="BT16" s="3"/>
       <c r="BU16" s="3"/>
       <c r="BV16" s="3"/>
@@ -2894,12 +3702,12 @@
       <c r="BY16" s="3"/>
       <c r="BZ16" s="3"/>
       <c r="CA16" s="3"/>
-      <c r="CB16" s="13"/>
+      <c r="CB16" s="15"/>
       <c r="CC16" s="3"/>
       <c r="CD16" s="3"/>
       <c r="CE16" s="3"/>
       <c r="CF16" s="3"/>
-      <c r="CG16" s="23"/>
+      <c r="CG16" s="28"/>
       <c r="CH16" s="3"/>
       <c r="CI16" s="3"/>
       <c r="CJ16" s="6"/>
@@ -2910,7 +3718,7 @@
       <c r="CO16" s="6"/>
       <c r="CP16" s="3"/>
       <c r="CQ16" s="4"/>
-      <c r="CR16" s="13"/>
+      <c r="CR16" s="15"/>
       <c r="CS16" s="3"/>
       <c r="CT16" s="3"/>
       <c r="CU16" s="3"/>
@@ -2921,10 +3729,10 @@
       <c r="CZ16" s="8"/>
       <c r="DA16" s="3"/>
       <c r="DB16" s="3"/>
-      <c r="DC16" s="14"/>
-      <c r="DD16" s="14"/>
-    </row>
-    <row r="17" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC16" s="17"/>
+      <c r="DD16" s="17"/>
+    </row>
+    <row r="17" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2935,11 +3743,11 @@
       <c r="H17" s="5"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="K17" s="15"/>
+      <c r="K17" s="18"/>
       <c r="L17" s="7"/>
       <c r="M17" s="4"/>
       <c r="N17" s="6"/>
-      <c r="O17" s="21"/>
+      <c r="O17" s="26"/>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -2977,23 +3785,23 @@
       <c r="AY17" s="4"/>
       <c r="AZ17" s="3"/>
       <c r="BA17" s="4"/>
-      <c r="BB17" s="22"/>
+      <c r="BB17" s="27"/>
       <c r="BC17" s="3"/>
       <c r="BD17" s="3"/>
       <c r="BE17" s="3"/>
       <c r="BF17" s="3"/>
-      <c r="BG17" s="13"/>
+      <c r="BG17" s="15"/>
       <c r="BH17" s="4"/>
       <c r="BI17" s="3"/>
       <c r="BJ17" s="3"/>
-      <c r="BL17" s="12"/>
-      <c r="BM17" s="12"/>
-      <c r="BN17" s="13"/>
+      <c r="BL17" s="14"/>
+      <c r="BM17" s="14"/>
+      <c r="BN17" s="15"/>
       <c r="BO17" s="3"/>
       <c r="BP17" s="3"/>
-      <c r="BQ17" s="13"/>
+      <c r="BQ17" s="15"/>
       <c r="BR17" s="6"/>
-      <c r="BS17" s="14"/>
+      <c r="BS17" s="17"/>
       <c r="BT17" s="3"/>
       <c r="BU17" s="3"/>
       <c r="BV17" s="3"/>
@@ -3002,12 +3810,12 @@
       <c r="BY17" s="3"/>
       <c r="BZ17" s="3"/>
       <c r="CA17" s="3"/>
-      <c r="CB17" s="13"/>
+      <c r="CB17" s="15"/>
       <c r="CC17" s="3"/>
       <c r="CD17" s="3"/>
       <c r="CE17" s="3"/>
       <c r="CF17" s="3"/>
-      <c r="CG17" s="23"/>
+      <c r="CG17" s="28"/>
       <c r="CH17" s="3"/>
       <c r="CI17" s="3"/>
       <c r="CJ17" s="6"/>
@@ -3018,7 +3826,7 @@
       <c r="CO17" s="6"/>
       <c r="CP17" s="3"/>
       <c r="CQ17" s="4"/>
-      <c r="CR17" s="13"/>
+      <c r="CR17" s="15"/>
       <c r="CS17" s="3"/>
       <c r="CT17" s="3"/>
       <c r="CU17" s="3"/>
@@ -3029,10 +3837,10 @@
       <c r="CZ17" s="8"/>
       <c r="DA17" s="3"/>
       <c r="DB17" s="3"/>
-      <c r="DC17" s="14"/>
-      <c r="DD17" s="14"/>
-    </row>
-    <row r="18" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC17" s="17"/>
+      <c r="DD17" s="17"/>
+    </row>
+    <row r="18" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -3043,11 +3851,11 @@
       <c r="H18" s="5"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="K18" s="15"/>
+      <c r="K18" s="18"/>
       <c r="L18" s="7"/>
       <c r="M18" s="4"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="21"/>
+      <c r="O18" s="26"/>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -3085,23 +3893,23 @@
       <c r="AY18" s="4"/>
       <c r="AZ18" s="3"/>
       <c r="BA18" s="4"/>
-      <c r="BB18" s="22"/>
+      <c r="BB18" s="27"/>
       <c r="BC18" s="3"/>
       <c r="BD18" s="3"/>
       <c r="BE18" s="3"/>
       <c r="BF18" s="3"/>
-      <c r="BG18" s="13"/>
+      <c r="BG18" s="15"/>
       <c r="BH18" s="4"/>
       <c r="BI18" s="3"/>
       <c r="BJ18" s="3"/>
-      <c r="BL18" s="12"/>
-      <c r="BM18" s="12"/>
-      <c r="BN18" s="13"/>
+      <c r="BL18" s="14"/>
+      <c r="BM18" s="14"/>
+      <c r="BN18" s="15"/>
       <c r="BO18" s="3"/>
       <c r="BP18" s="3"/>
-      <c r="BQ18" s="13"/>
+      <c r="BQ18" s="15"/>
       <c r="BR18" s="6"/>
-      <c r="BS18" s="14"/>
+      <c r="BS18" s="17"/>
       <c r="BT18" s="3"/>
       <c r="BU18" s="3"/>
       <c r="BV18" s="3"/>
@@ -3110,12 +3918,12 @@
       <c r="BY18" s="3"/>
       <c r="BZ18" s="3"/>
       <c r="CA18" s="3"/>
-      <c r="CB18" s="13"/>
+      <c r="CB18" s="15"/>
       <c r="CC18" s="3"/>
       <c r="CD18" s="3"/>
       <c r="CE18" s="3"/>
       <c r="CF18" s="3"/>
-      <c r="CG18" s="23"/>
+      <c r="CG18" s="28"/>
       <c r="CH18" s="3"/>
       <c r="CI18" s="3"/>
       <c r="CJ18" s="6"/>
@@ -3126,7 +3934,7 @@
       <c r="CO18" s="6"/>
       <c r="CP18" s="3"/>
       <c r="CQ18" s="4"/>
-      <c r="CR18" s="13"/>
+      <c r="CR18" s="15"/>
       <c r="CS18" s="3"/>
       <c r="CT18" s="3"/>
       <c r="CU18" s="3"/>
@@ -3137,10 +3945,10 @@
       <c r="CZ18" s="8"/>
       <c r="DA18" s="3"/>
       <c r="DB18" s="3"/>
-      <c r="DC18" s="14"/>
-      <c r="DD18" s="14"/>
-    </row>
-    <row r="19" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC18" s="17"/>
+      <c r="DD18" s="17"/>
+    </row>
+    <row r="19" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -3151,11 +3959,11 @@
       <c r="H19" s="5"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="15"/>
+      <c r="K19" s="18"/>
       <c r="L19" s="7"/>
       <c r="M19" s="4"/>
       <c r="N19" s="6"/>
-      <c r="O19" s="21"/>
+      <c r="O19" s="26"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -3193,23 +4001,23 @@
       <c r="AY19" s="4"/>
       <c r="AZ19" s="3"/>
       <c r="BA19" s="4"/>
-      <c r="BB19" s="22"/>
+      <c r="BB19" s="27"/>
       <c r="BC19" s="3"/>
       <c r="BD19" s="3"/>
       <c r="BE19" s="3"/>
       <c r="BF19" s="3"/>
-      <c r="BG19" s="13"/>
+      <c r="BG19" s="15"/>
       <c r="BH19" s="4"/>
       <c r="BI19" s="3"/>
       <c r="BJ19" s="3"/>
-      <c r="BL19" s="12"/>
-      <c r="BM19" s="12"/>
-      <c r="BN19" s="13"/>
+      <c r="BL19" s="14"/>
+      <c r="BM19" s="14"/>
+      <c r="BN19" s="15"/>
       <c r="BO19" s="3"/>
       <c r="BP19" s="3"/>
-      <c r="BQ19" s="13"/>
+      <c r="BQ19" s="15"/>
       <c r="BR19" s="6"/>
-      <c r="BS19" s="14"/>
+      <c r="BS19" s="17"/>
       <c r="BT19" s="3"/>
       <c r="BU19" s="3"/>
       <c r="BV19" s="3"/>
@@ -3218,12 +4026,12 @@
       <c r="BY19" s="3"/>
       <c r="BZ19" s="3"/>
       <c r="CA19" s="3"/>
-      <c r="CB19" s="13"/>
+      <c r="CB19" s="15"/>
       <c r="CC19" s="3"/>
       <c r="CD19" s="3"/>
       <c r="CE19" s="3"/>
       <c r="CF19" s="3"/>
-      <c r="CG19" s="23"/>
+      <c r="CG19" s="28"/>
       <c r="CH19" s="3"/>
       <c r="CI19" s="3"/>
       <c r="CJ19" s="6"/>
@@ -3234,7 +4042,7 @@
       <c r="CO19" s="6"/>
       <c r="CP19" s="3"/>
       <c r="CQ19" s="4"/>
-      <c r="CR19" s="13"/>
+      <c r="CR19" s="15"/>
       <c r="CS19" s="3"/>
       <c r="CT19" s="3"/>
       <c r="CU19" s="3"/>
@@ -3245,10 +4053,10 @@
       <c r="CZ19" s="8"/>
       <c r="DA19" s="3"/>
       <c r="DB19" s="3"/>
-      <c r="DC19" s="14"/>
-      <c r="DD19" s="14"/>
-    </row>
-    <row r="20" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC19" s="17"/>
+      <c r="DD19" s="17"/>
+    </row>
+    <row r="20" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -3259,11 +4067,11 @@
       <c r="H20" s="5"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
-      <c r="K20" s="15"/>
+      <c r="K20" s="18"/>
       <c r="L20" s="7"/>
       <c r="M20" s="4"/>
       <c r="N20" s="6"/>
-      <c r="O20" s="21"/>
+      <c r="O20" s="26"/>
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
@@ -3301,23 +4109,23 @@
       <c r="AY20" s="4"/>
       <c r="AZ20" s="3"/>
       <c r="BA20" s="4"/>
-      <c r="BB20" s="22"/>
+      <c r="BB20" s="27"/>
       <c r="BC20" s="3"/>
       <c r="BD20" s="3"/>
       <c r="BE20" s="3"/>
       <c r="BF20" s="3"/>
-      <c r="BG20" s="13"/>
+      <c r="BG20" s="15"/>
       <c r="BH20" s="4"/>
       <c r="BI20" s="3"/>
       <c r="BJ20" s="3"/>
-      <c r="BL20" s="12"/>
-      <c r="BM20" s="12"/>
-      <c r="BN20" s="13"/>
+      <c r="BL20" s="14"/>
+      <c r="BM20" s="14"/>
+      <c r="BN20" s="15"/>
       <c r="BO20" s="3"/>
       <c r="BP20" s="3"/>
-      <c r="BQ20" s="13"/>
+      <c r="BQ20" s="15"/>
       <c r="BR20" s="6"/>
-      <c r="BS20" s="14"/>
+      <c r="BS20" s="17"/>
       <c r="BT20" s="3"/>
       <c r="BU20" s="3"/>
       <c r="BV20" s="3"/>
@@ -3326,12 +4134,12 @@
       <c r="BY20" s="3"/>
       <c r="BZ20" s="3"/>
       <c r="CA20" s="3"/>
-      <c r="CB20" s="13"/>
+      <c r="CB20" s="15"/>
       <c r="CC20" s="3"/>
       <c r="CD20" s="3"/>
       <c r="CE20" s="3"/>
       <c r="CF20" s="3"/>
-      <c r="CG20" s="23"/>
+      <c r="CG20" s="28"/>
       <c r="CH20" s="3"/>
       <c r="CI20" s="3"/>
       <c r="CJ20" s="6"/>
@@ -3342,7 +4150,7 @@
       <c r="CO20" s="6"/>
       <c r="CP20" s="3"/>
       <c r="CQ20" s="4"/>
-      <c r="CR20" s="13"/>
+      <c r="CR20" s="15"/>
       <c r="CS20" s="3"/>
       <c r="CT20" s="3"/>
       <c r="CU20" s="3"/>
@@ -3353,10 +4161,10 @@
       <c r="CZ20" s="8"/>
       <c r="DA20" s="3"/>
       <c r="DB20" s="3"/>
-      <c r="DC20" s="14"/>
-      <c r="DD20" s="14"/>
-    </row>
-    <row r="21" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC20" s="17"/>
+      <c r="DD20" s="17"/>
+    </row>
+    <row r="21" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -3367,11 +4175,11 @@
       <c r="H21" s="5"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
-      <c r="K21" s="15"/>
+      <c r="K21" s="18"/>
       <c r="L21" s="7"/>
       <c r="M21" s="4"/>
       <c r="N21" s="6"/>
-      <c r="O21" s="21"/>
+      <c r="O21" s="26"/>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
@@ -3409,23 +4217,23 @@
       <c r="AY21" s="4"/>
       <c r="AZ21" s="3"/>
       <c r="BA21" s="4"/>
-      <c r="BB21" s="22"/>
+      <c r="BB21" s="27"/>
       <c r="BC21" s="3"/>
       <c r="BD21" s="3"/>
       <c r="BE21" s="3"/>
       <c r="BF21" s="3"/>
-      <c r="BG21" s="13"/>
+      <c r="BG21" s="15"/>
       <c r="BH21" s="4"/>
       <c r="BI21" s="3"/>
       <c r="BJ21" s="3"/>
-      <c r="BL21" s="12"/>
-      <c r="BM21" s="12"/>
-      <c r="BN21" s="13"/>
+      <c r="BL21" s="14"/>
+      <c r="BM21" s="14"/>
+      <c r="BN21" s="15"/>
       <c r="BO21" s="3"/>
       <c r="BP21" s="3"/>
-      <c r="BQ21" s="13"/>
+      <c r="BQ21" s="15"/>
       <c r="BR21" s="6"/>
-      <c r="BS21" s="14"/>
+      <c r="BS21" s="17"/>
       <c r="BT21" s="3"/>
       <c r="BU21" s="3"/>
       <c r="BV21" s="3"/>
@@ -3434,12 +4242,12 @@
       <c r="BY21" s="3"/>
       <c r="BZ21" s="3"/>
       <c r="CA21" s="3"/>
-      <c r="CB21" s="13"/>
+      <c r="CB21" s="15"/>
       <c r="CC21" s="3"/>
       <c r="CD21" s="3"/>
       <c r="CE21" s="3"/>
       <c r="CF21" s="3"/>
-      <c r="CG21" s="23"/>
+      <c r="CG21" s="28"/>
       <c r="CH21" s="3"/>
       <c r="CI21" s="3"/>
       <c r="CJ21" s="6"/>
@@ -3450,7 +4258,7 @@
       <c r="CO21" s="6"/>
       <c r="CP21" s="3"/>
       <c r="CQ21" s="4"/>
-      <c r="CR21" s="13"/>
+      <c r="CR21" s="15"/>
       <c r="CS21" s="3"/>
       <c r="CT21" s="3"/>
       <c r="CU21" s="3"/>
@@ -3461,10 +4269,10 @@
       <c r="CZ21" s="8"/>
       <c r="DA21" s="3"/>
       <c r="DB21" s="3"/>
-      <c r="DC21" s="14"/>
-      <c r="DD21" s="14"/>
-    </row>
-    <row r="22" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC21" s="17"/>
+      <c r="DD21" s="17"/>
+    </row>
+    <row r="22" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -3475,11 +4283,11 @@
       <c r="H22" s="5"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
-      <c r="K22" s="15"/>
+      <c r="K22" s="18"/>
       <c r="L22" s="7"/>
       <c r="M22" s="4"/>
       <c r="N22" s="6"/>
-      <c r="O22" s="21"/>
+      <c r="O22" s="26"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
@@ -3517,23 +4325,23 @@
       <c r="AY22" s="4"/>
       <c r="AZ22" s="3"/>
       <c r="BA22" s="4"/>
-      <c r="BB22" s="22"/>
+      <c r="BB22" s="27"/>
       <c r="BC22" s="3"/>
       <c r="BD22" s="3"/>
       <c r="BE22" s="3"/>
       <c r="BF22" s="3"/>
-      <c r="BG22" s="13"/>
+      <c r="BG22" s="15"/>
       <c r="BH22" s="4"/>
       <c r="BI22" s="3"/>
       <c r="BJ22" s="3"/>
-      <c r="BL22" s="12"/>
-      <c r="BM22" s="12"/>
-      <c r="BN22" s="13"/>
+      <c r="BL22" s="14"/>
+      <c r="BM22" s="14"/>
+      <c r="BN22" s="15"/>
       <c r="BO22" s="3"/>
       <c r="BP22" s="3"/>
-      <c r="BQ22" s="13"/>
+      <c r="BQ22" s="15"/>
       <c r="BR22" s="6"/>
-      <c r="BS22" s="14"/>
+      <c r="BS22" s="17"/>
       <c r="BT22" s="3"/>
       <c r="BU22" s="3"/>
       <c r="BV22" s="3"/>
@@ -3542,12 +4350,12 @@
       <c r="BY22" s="3"/>
       <c r="BZ22" s="3"/>
       <c r="CA22" s="3"/>
-      <c r="CB22" s="13"/>
+      <c r="CB22" s="15"/>
       <c r="CC22" s="3"/>
       <c r="CD22" s="3"/>
       <c r="CE22" s="3"/>
       <c r="CF22" s="3"/>
-      <c r="CG22" s="23"/>
+      <c r="CG22" s="28"/>
       <c r="CH22" s="3"/>
       <c r="CI22" s="3"/>
       <c r="CJ22" s="6"/>
@@ -3558,7 +4366,7 @@
       <c r="CO22" s="6"/>
       <c r="CP22" s="3"/>
       <c r="CQ22" s="4"/>
-      <c r="CR22" s="13"/>
+      <c r="CR22" s="15"/>
       <c r="CS22" s="3"/>
       <c r="CT22" s="3"/>
       <c r="CU22" s="3"/>
@@ -3569,10 +4377,10 @@
       <c r="CZ22" s="8"/>
       <c r="DA22" s="3"/>
       <c r="DB22" s="3"/>
-      <c r="DC22" s="14"/>
-      <c r="DD22" s="14"/>
-    </row>
-    <row r="23" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC22" s="17"/>
+      <c r="DD22" s="17"/>
+    </row>
+    <row r="23" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -3583,11 +4391,11 @@
       <c r="H23" s="5"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
-      <c r="K23" s="15"/>
+      <c r="K23" s="18"/>
       <c r="L23" s="7"/>
       <c r="M23" s="4"/>
       <c r="N23" s="6"/>
-      <c r="O23" s="21"/>
+      <c r="O23" s="26"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -3625,23 +4433,23 @@
       <c r="AY23" s="4"/>
       <c r="AZ23" s="3"/>
       <c r="BA23" s="4"/>
-      <c r="BB23" s="22"/>
+      <c r="BB23" s="27"/>
       <c r="BC23" s="3"/>
       <c r="BD23" s="3"/>
       <c r="BE23" s="3"/>
       <c r="BF23" s="3"/>
-      <c r="BG23" s="13"/>
+      <c r="BG23" s="15"/>
       <c r="BH23" s="4"/>
       <c r="BI23" s="3"/>
       <c r="BJ23" s="3"/>
-      <c r="BL23" s="12"/>
-      <c r="BM23" s="12"/>
-      <c r="BN23" s="13"/>
+      <c r="BL23" s="14"/>
+      <c r="BM23" s="14"/>
+      <c r="BN23" s="15"/>
       <c r="BO23" s="3"/>
       <c r="BP23" s="3"/>
-      <c r="BQ23" s="13"/>
+      <c r="BQ23" s="15"/>
       <c r="BR23" s="6"/>
-      <c r="BS23" s="14"/>
+      <c r="BS23" s="17"/>
       <c r="BT23" s="3"/>
       <c r="BU23" s="3"/>
       <c r="BV23" s="3"/>
@@ -3650,12 +4458,12 @@
       <c r="BY23" s="3"/>
       <c r="BZ23" s="3"/>
       <c r="CA23" s="3"/>
-      <c r="CB23" s="13"/>
+      <c r="CB23" s="15"/>
       <c r="CC23" s="3"/>
       <c r="CD23" s="3"/>
       <c r="CE23" s="3"/>
       <c r="CF23" s="3"/>
-      <c r="CG23" s="23"/>
+      <c r="CG23" s="28"/>
       <c r="CH23" s="3"/>
       <c r="CI23" s="3"/>
       <c r="CJ23" s="6"/>
@@ -3666,7 +4474,7 @@
       <c r="CO23" s="6"/>
       <c r="CP23" s="3"/>
       <c r="CQ23" s="4"/>
-      <c r="CR23" s="13"/>
+      <c r="CR23" s="15"/>
       <c r="CS23" s="3"/>
       <c r="CT23" s="3"/>
       <c r="CU23" s="3"/>
@@ -3677,10 +4485,10 @@
       <c r="CZ23" s="8"/>
       <c r="DA23" s="3"/>
       <c r="DB23" s="3"/>
-      <c r="DC23" s="14"/>
-      <c r="DD23" s="14"/>
-    </row>
-    <row r="24" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC23" s="17"/>
+      <c r="DD23" s="17"/>
+    </row>
+    <row r="24" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -3691,11 +4499,11 @@
       <c r="H24" s="5"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
-      <c r="K24" s="15"/>
+      <c r="K24" s="18"/>
       <c r="L24" s="7"/>
       <c r="M24" s="4"/>
       <c r="N24" s="6"/>
-      <c r="O24" s="21"/>
+      <c r="O24" s="26"/>
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
@@ -3733,23 +4541,23 @@
       <c r="AY24" s="4"/>
       <c r="AZ24" s="3"/>
       <c r="BA24" s="4"/>
-      <c r="BB24" s="22"/>
+      <c r="BB24" s="27"/>
       <c r="BC24" s="3"/>
       <c r="BD24" s="3"/>
       <c r="BE24" s="3"/>
       <c r="BF24" s="3"/>
-      <c r="BG24" s="13"/>
+      <c r="BG24" s="15"/>
       <c r="BH24" s="4"/>
       <c r="BI24" s="3"/>
       <c r="BJ24" s="3"/>
-      <c r="BL24" s="12"/>
-      <c r="BM24" s="12"/>
-      <c r="BN24" s="13"/>
+      <c r="BL24" s="14"/>
+      <c r="BM24" s="14"/>
+      <c r="BN24" s="15"/>
       <c r="BO24" s="3"/>
       <c r="BP24" s="3"/>
-      <c r="BQ24" s="13"/>
+      <c r="BQ24" s="15"/>
       <c r="BR24" s="6"/>
-      <c r="BS24" s="14"/>
+      <c r="BS24" s="17"/>
       <c r="BT24" s="3"/>
       <c r="BU24" s="3"/>
       <c r="BV24" s="3"/>
@@ -3758,12 +4566,12 @@
       <c r="BY24" s="3"/>
       <c r="BZ24" s="3"/>
       <c r="CA24" s="3"/>
-      <c r="CB24" s="13"/>
+      <c r="CB24" s="15"/>
       <c r="CC24" s="3"/>
       <c r="CD24" s="3"/>
       <c r="CE24" s="3"/>
       <c r="CF24" s="3"/>
-      <c r="CG24" s="23"/>
+      <c r="CG24" s="28"/>
       <c r="CH24" s="3"/>
       <c r="CI24" s="3"/>
       <c r="CJ24" s="6"/>
@@ -3774,7 +4582,7 @@
       <c r="CO24" s="6"/>
       <c r="CP24" s="3"/>
       <c r="CQ24" s="4"/>
-      <c r="CR24" s="13"/>
+      <c r="CR24" s="15"/>
       <c r="CS24" s="3"/>
       <c r="CT24" s="3"/>
       <c r="CU24" s="3"/>
@@ -3785,10 +4593,10 @@
       <c r="CZ24" s="8"/>
       <c r="DA24" s="3"/>
       <c r="DB24" s="3"/>
-      <c r="DC24" s="14"/>
-      <c r="DD24" s="14"/>
-    </row>
-    <row r="25" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC24" s="17"/>
+      <c r="DD24" s="17"/>
+    </row>
+    <row r="25" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -3799,11 +4607,11 @@
       <c r="H25" s="5"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="15"/>
+      <c r="K25" s="18"/>
       <c r="L25" s="7"/>
       <c r="M25" s="4"/>
       <c r="N25" s="6"/>
-      <c r="O25" s="21"/>
+      <c r="O25" s="26"/>
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
@@ -3841,23 +4649,23 @@
       <c r="AY25" s="4"/>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="4"/>
-      <c r="BB25" s="22"/>
+      <c r="BB25" s="27"/>
       <c r="BC25" s="3"/>
       <c r="BD25" s="3"/>
       <c r="BE25" s="3"/>
       <c r="BF25" s="3"/>
-      <c r="BG25" s="13"/>
+      <c r="BG25" s="15"/>
       <c r="BH25" s="4"/>
       <c r="BI25" s="3"/>
       <c r="BJ25" s="3"/>
-      <c r="BL25" s="12"/>
-      <c r="BM25" s="12"/>
-      <c r="BN25" s="13"/>
+      <c r="BL25" s="14"/>
+      <c r="BM25" s="14"/>
+      <c r="BN25" s="15"/>
       <c r="BO25" s="3"/>
       <c r="BP25" s="3"/>
-      <c r="BQ25" s="13"/>
+      <c r="BQ25" s="15"/>
       <c r="BR25" s="6"/>
-      <c r="BS25" s="14"/>
+      <c r="BS25" s="17"/>
       <c r="BT25" s="3"/>
       <c r="BU25" s="3"/>
       <c r="BV25" s="3"/>
@@ -3866,12 +4674,12 @@
       <c r="BY25" s="3"/>
       <c r="BZ25" s="3"/>
       <c r="CA25" s="3"/>
-      <c r="CB25" s="13"/>
+      <c r="CB25" s="15"/>
       <c r="CC25" s="3"/>
       <c r="CD25" s="3"/>
       <c r="CE25" s="3"/>
       <c r="CF25" s="3"/>
-      <c r="CG25" s="23"/>
+      <c r="CG25" s="28"/>
       <c r="CH25" s="3"/>
       <c r="CI25" s="3"/>
       <c r="CJ25" s="6"/>
@@ -3882,7 +4690,7 @@
       <c r="CO25" s="6"/>
       <c r="CP25" s="3"/>
       <c r="CQ25" s="4"/>
-      <c r="CR25" s="13"/>
+      <c r="CR25" s="15"/>
       <c r="CS25" s="3"/>
       <c r="CT25" s="3"/>
       <c r="CU25" s="3"/>
@@ -3893,10 +4701,10 @@
       <c r="CZ25" s="8"/>
       <c r="DA25" s="3"/>
       <c r="DB25" s="3"/>
-      <c r="DC25" s="14"/>
-      <c r="DD25" s="14"/>
-    </row>
-    <row r="26" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC25" s="17"/>
+      <c r="DD25" s="17"/>
+    </row>
+    <row r="26" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -3907,11 +4715,11 @@
       <c r="H26" s="5"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
-      <c r="K26" s="15"/>
+      <c r="K26" s="18"/>
       <c r="L26" s="7"/>
       <c r="M26" s="4"/>
       <c r="N26" s="6"/>
-      <c r="O26" s="21"/>
+      <c r="O26" s="26"/>
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -3949,23 +4757,23 @@
       <c r="AY26" s="4"/>
       <c r="AZ26" s="3"/>
       <c r="BA26" s="4"/>
-      <c r="BB26" s="22"/>
+      <c r="BB26" s="27"/>
       <c r="BC26" s="3"/>
       <c r="BD26" s="3"/>
       <c r="BE26" s="3"/>
       <c r="BF26" s="3"/>
-      <c r="BG26" s="13"/>
+      <c r="BG26" s="15"/>
       <c r="BH26" s="4"/>
       <c r="BI26" s="3"/>
       <c r="BJ26" s="3"/>
-      <c r="BL26" s="12"/>
-      <c r="BM26" s="12"/>
-      <c r="BN26" s="13"/>
+      <c r="BL26" s="14"/>
+      <c r="BM26" s="14"/>
+      <c r="BN26" s="15"/>
       <c r="BO26" s="3"/>
       <c r="BP26" s="3"/>
-      <c r="BQ26" s="13"/>
+      <c r="BQ26" s="15"/>
       <c r="BR26" s="6"/>
-      <c r="BS26" s="14"/>
+      <c r="BS26" s="17"/>
       <c r="BT26" s="3"/>
       <c r="BU26" s="3"/>
       <c r="BV26" s="3"/>
@@ -3974,12 +4782,12 @@
       <c r="BY26" s="3"/>
       <c r="BZ26" s="3"/>
       <c r="CA26" s="3"/>
-      <c r="CB26" s="13"/>
+      <c r="CB26" s="15"/>
       <c r="CC26" s="3"/>
       <c r="CD26" s="3"/>
       <c r="CE26" s="3"/>
       <c r="CF26" s="3"/>
-      <c r="CG26" s="23"/>
+      <c r="CG26" s="28"/>
       <c r="CH26" s="3"/>
       <c r="CI26" s="3"/>
       <c r="CJ26" s="6"/>
@@ -3990,7 +4798,7 @@
       <c r="CO26" s="6"/>
       <c r="CP26" s="3"/>
       <c r="CQ26" s="4"/>
-      <c r="CR26" s="13"/>
+      <c r="CR26" s="15"/>
       <c r="CS26" s="3"/>
       <c r="CT26" s="3"/>
       <c r="CU26" s="3"/>
@@ -4001,10 +4809,10 @@
       <c r="CZ26" s="8"/>
       <c r="DA26" s="3"/>
       <c r="DB26" s="3"/>
-      <c r="DC26" s="14"/>
-      <c r="DD26" s="14"/>
-    </row>
-    <row r="27" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC26" s="17"/>
+      <c r="DD26" s="17"/>
+    </row>
+    <row r="27" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -4015,11 +4823,11 @@
       <c r="H27" s="5"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
-      <c r="K27" s="15"/>
+      <c r="K27" s="18"/>
       <c r="L27" s="7"/>
       <c r="M27" s="4"/>
       <c r="N27" s="6"/>
-      <c r="O27" s="21"/>
+      <c r="O27" s="26"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
@@ -4057,23 +4865,23 @@
       <c r="AY27" s="4"/>
       <c r="AZ27" s="3"/>
       <c r="BA27" s="4"/>
-      <c r="BB27" s="22"/>
+      <c r="BB27" s="27"/>
       <c r="BC27" s="3"/>
       <c r="BD27" s="3"/>
       <c r="BE27" s="3"/>
       <c r="BF27" s="3"/>
-      <c r="BG27" s="13"/>
+      <c r="BG27" s="15"/>
       <c r="BH27" s="4"/>
       <c r="BI27" s="3"/>
       <c r="BJ27" s="3"/>
-      <c r="BL27" s="12"/>
-      <c r="BM27" s="12"/>
-      <c r="BN27" s="13"/>
+      <c r="BL27" s="14"/>
+      <c r="BM27" s="14"/>
+      <c r="BN27" s="15"/>
       <c r="BO27" s="3"/>
       <c r="BP27" s="3"/>
-      <c r="BQ27" s="13"/>
+      <c r="BQ27" s="15"/>
       <c r="BR27" s="6"/>
-      <c r="BS27" s="14"/>
+      <c r="BS27" s="17"/>
       <c r="BT27" s="3"/>
       <c r="BU27" s="3"/>
       <c r="BV27" s="3"/>
@@ -4082,12 +4890,12 @@
       <c r="BY27" s="3"/>
       <c r="BZ27" s="3"/>
       <c r="CA27" s="3"/>
-      <c r="CB27" s="13"/>
+      <c r="CB27" s="15"/>
       <c r="CC27" s="3"/>
       <c r="CD27" s="3"/>
       <c r="CE27" s="3"/>
       <c r="CF27" s="3"/>
-      <c r="CG27" s="23"/>
+      <c r="CG27" s="28"/>
       <c r="CH27" s="3"/>
       <c r="CI27" s="3"/>
       <c r="CJ27" s="6"/>
@@ -4098,7 +4906,7 @@
       <c r="CO27" s="6"/>
       <c r="CP27" s="3"/>
       <c r="CQ27" s="4"/>
-      <c r="CR27" s="13"/>
+      <c r="CR27" s="15"/>
       <c r="CS27" s="3"/>
       <c r="CT27" s="3"/>
       <c r="CU27" s="3"/>
@@ -4109,10 +4917,10 @@
       <c r="CZ27" s="8"/>
       <c r="DA27" s="3"/>
       <c r="DB27" s="3"/>
-      <c r="DC27" s="14"/>
-      <c r="DD27" s="14"/>
-    </row>
-    <row r="28" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC27" s="17"/>
+      <c r="DD27" s="17"/>
+    </row>
+    <row r="28" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -4123,11 +4931,11 @@
       <c r="H28" s="5"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
-      <c r="K28" s="15"/>
+      <c r="K28" s="18"/>
       <c r="L28" s="7"/>
       <c r="M28" s="4"/>
       <c r="N28" s="6"/>
-      <c r="O28" s="21"/>
+      <c r="O28" s="26"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -4165,23 +4973,23 @@
       <c r="AY28" s="4"/>
       <c r="AZ28" s="3"/>
       <c r="BA28" s="4"/>
-      <c r="BB28" s="22"/>
+      <c r="BB28" s="27"/>
       <c r="BC28" s="3"/>
       <c r="BD28" s="3"/>
       <c r="BE28" s="3"/>
       <c r="BF28" s="3"/>
-      <c r="BG28" s="13"/>
+      <c r="BG28" s="15"/>
       <c r="BH28" s="4"/>
       <c r="BI28" s="3"/>
       <c r="BJ28" s="3"/>
-      <c r="BL28" s="12"/>
-      <c r="BM28" s="12"/>
-      <c r="BN28" s="13"/>
+      <c r="BL28" s="14"/>
+      <c r="BM28" s="14"/>
+      <c r="BN28" s="15"/>
       <c r="BO28" s="3"/>
       <c r="BP28" s="3"/>
-      <c r="BQ28" s="13"/>
+      <c r="BQ28" s="15"/>
       <c r="BR28" s="6"/>
-      <c r="BS28" s="14"/>
+      <c r="BS28" s="17"/>
       <c r="BT28" s="3"/>
       <c r="BU28" s="3"/>
       <c r="BV28" s="3"/>
@@ -4190,12 +4998,12 @@
       <c r="BY28" s="3"/>
       <c r="BZ28" s="3"/>
       <c r="CA28" s="3"/>
-      <c r="CB28" s="13"/>
+      <c r="CB28" s="15"/>
       <c r="CC28" s="3"/>
       <c r="CD28" s="3"/>
       <c r="CE28" s="3"/>
       <c r="CF28" s="3"/>
-      <c r="CG28" s="23"/>
+      <c r="CG28" s="28"/>
       <c r="CH28" s="3"/>
       <c r="CI28" s="3"/>
       <c r="CJ28" s="6"/>
@@ -4206,7 +5014,7 @@
       <c r="CO28" s="6"/>
       <c r="CP28" s="3"/>
       <c r="CQ28" s="4"/>
-      <c r="CR28" s="13"/>
+      <c r="CR28" s="15"/>
       <c r="CS28" s="3"/>
       <c r="CT28" s="3"/>
       <c r="CU28" s="3"/>
@@ -4217,10 +5025,10 @@
       <c r="CZ28" s="8"/>
       <c r="DA28" s="3"/>
       <c r="DB28" s="3"/>
-      <c r="DC28" s="14"/>
-      <c r="DD28" s="14"/>
-    </row>
-    <row r="29" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC28" s="17"/>
+      <c r="DD28" s="17"/>
+    </row>
+    <row r="29" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -4231,11 +5039,11 @@
       <c r="H29" s="5"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
-      <c r="K29" s="15"/>
+      <c r="K29" s="18"/>
       <c r="L29" s="7"/>
       <c r="M29" s="4"/>
       <c r="N29" s="6"/>
-      <c r="O29" s="21"/>
+      <c r="O29" s="26"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -4273,23 +5081,23 @@
       <c r="AY29" s="4"/>
       <c r="AZ29" s="3"/>
       <c r="BA29" s="4"/>
-      <c r="BB29" s="22"/>
+      <c r="BB29" s="27"/>
       <c r="BC29" s="3"/>
       <c r="BD29" s="3"/>
       <c r="BE29" s="3"/>
       <c r="BF29" s="3"/>
-      <c r="BG29" s="13"/>
+      <c r="BG29" s="15"/>
       <c r="BH29" s="4"/>
       <c r="BI29" s="3"/>
       <c r="BJ29" s="3"/>
-      <c r="BL29" s="12"/>
-      <c r="BM29" s="12"/>
-      <c r="BN29" s="13"/>
+      <c r="BL29" s="14"/>
+      <c r="BM29" s="14"/>
+      <c r="BN29" s="15"/>
       <c r="BO29" s="3"/>
       <c r="BP29" s="3"/>
-      <c r="BQ29" s="13"/>
+      <c r="BQ29" s="15"/>
       <c r="BR29" s="6"/>
-      <c r="BS29" s="14"/>
+      <c r="BS29" s="17"/>
       <c r="BT29" s="3"/>
       <c r="BU29" s="3"/>
       <c r="BV29" s="3"/>
@@ -4298,12 +5106,12 @@
       <c r="BY29" s="3"/>
       <c r="BZ29" s="3"/>
       <c r="CA29" s="3"/>
-      <c r="CB29" s="13"/>
+      <c r="CB29" s="15"/>
       <c r="CC29" s="3"/>
       <c r="CD29" s="3"/>
       <c r="CE29" s="3"/>
       <c r="CF29" s="3"/>
-      <c r="CG29" s="23"/>
+      <c r="CG29" s="28"/>
       <c r="CH29" s="3"/>
       <c r="CI29" s="3"/>
       <c r="CJ29" s="6"/>
@@ -4314,7 +5122,7 @@
       <c r="CO29" s="6"/>
       <c r="CP29" s="3"/>
       <c r="CQ29" s="4"/>
-      <c r="CR29" s="13"/>
+      <c r="CR29" s="15"/>
       <c r="CS29" s="3"/>
       <c r="CT29" s="3"/>
       <c r="CU29" s="3"/>
@@ -4325,10 +5133,10 @@
       <c r="CZ29" s="8"/>
       <c r="DA29" s="3"/>
       <c r="DB29" s="3"/>
-      <c r="DC29" s="14"/>
-      <c r="DD29" s="14"/>
-    </row>
-    <row r="30" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC29" s="17"/>
+      <c r="DD29" s="17"/>
+    </row>
+    <row r="30" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -4339,11 +5147,11 @@
       <c r="H30" s="5"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
-      <c r="K30" s="15"/>
+      <c r="K30" s="18"/>
       <c r="L30" s="7"/>
       <c r="M30" s="4"/>
       <c r="N30" s="6"/>
-      <c r="O30" s="21"/>
+      <c r="O30" s="26"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -4381,23 +5189,23 @@
       <c r="AY30" s="4"/>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="4"/>
-      <c r="BB30" s="22"/>
+      <c r="BB30" s="27"/>
       <c r="BC30" s="3"/>
       <c r="BD30" s="3"/>
       <c r="BE30" s="3"/>
       <c r="BF30" s="3"/>
-      <c r="BG30" s="13"/>
+      <c r="BG30" s="15"/>
       <c r="BH30" s="4"/>
       <c r="BI30" s="3"/>
       <c r="BJ30" s="3"/>
-      <c r="BL30" s="12"/>
-      <c r="BM30" s="12"/>
-      <c r="BN30" s="13"/>
+      <c r="BL30" s="14"/>
+      <c r="BM30" s="14"/>
+      <c r="BN30" s="15"/>
       <c r="BO30" s="3"/>
       <c r="BP30" s="3"/>
-      <c r="BQ30" s="13"/>
+      <c r="BQ30" s="15"/>
       <c r="BR30" s="6"/>
-      <c r="BS30" s="14"/>
+      <c r="BS30" s="17"/>
       <c r="BT30" s="3"/>
       <c r="BU30" s="3"/>
       <c r="BV30" s="3"/>
@@ -4406,12 +5214,12 @@
       <c r="BY30" s="3"/>
       <c r="BZ30" s="3"/>
       <c r="CA30" s="3"/>
-      <c r="CB30" s="13"/>
+      <c r="CB30" s="15"/>
       <c r="CC30" s="3"/>
       <c r="CD30" s="3"/>
       <c r="CE30" s="3"/>
       <c r="CF30" s="3"/>
-      <c r="CG30" s="23"/>
+      <c r="CG30" s="28"/>
       <c r="CH30" s="3"/>
       <c r="CI30" s="3"/>
       <c r="CJ30" s="6"/>
@@ -4422,7 +5230,7 @@
       <c r="CO30" s="6"/>
       <c r="CP30" s="3"/>
       <c r="CQ30" s="4"/>
-      <c r="CR30" s="13"/>
+      <c r="CR30" s="15"/>
       <c r="CS30" s="3"/>
       <c r="CT30" s="3"/>
       <c r="CU30" s="3"/>
@@ -4433,10 +5241,10 @@
       <c r="CZ30" s="8"/>
       <c r="DA30" s="3"/>
       <c r="DB30" s="3"/>
-      <c r="DC30" s="14"/>
-      <c r="DD30" s="14"/>
-    </row>
-    <row r="31" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC30" s="17"/>
+      <c r="DD30" s="17"/>
+    </row>
+    <row r="31" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -4447,11 +5255,11 @@
       <c r="H31" s="5"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
-      <c r="K31" s="15"/>
+      <c r="K31" s="18"/>
       <c r="L31" s="7"/>
       <c r="M31" s="4"/>
       <c r="N31" s="6"/>
-      <c r="O31" s="21"/>
+      <c r="O31" s="26"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -4489,23 +5297,23 @@
       <c r="AY31" s="4"/>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="4"/>
-      <c r="BB31" s="22"/>
+      <c r="BB31" s="27"/>
       <c r="BC31" s="3"/>
       <c r="BD31" s="3"/>
       <c r="BE31" s="3"/>
       <c r="BF31" s="3"/>
-      <c r="BG31" s="13"/>
+      <c r="BG31" s="15"/>
       <c r="BH31" s="4"/>
       <c r="BI31" s="3"/>
       <c r="BJ31" s="3"/>
-      <c r="BL31" s="12"/>
-      <c r="BM31" s="12"/>
-      <c r="BN31" s="13"/>
+      <c r="BL31" s="14"/>
+      <c r="BM31" s="14"/>
+      <c r="BN31" s="15"/>
       <c r="BO31" s="3"/>
       <c r="BP31" s="3"/>
-      <c r="BQ31" s="13"/>
+      <c r="BQ31" s="15"/>
       <c r="BR31" s="6"/>
-      <c r="BS31" s="14"/>
+      <c r="BS31" s="17"/>
       <c r="BT31" s="3"/>
       <c r="BU31" s="3"/>
       <c r="BV31" s="3"/>
@@ -4514,12 +5322,12 @@
       <c r="BY31" s="3"/>
       <c r="BZ31" s="3"/>
       <c r="CA31" s="3"/>
-      <c r="CB31" s="13"/>
+      <c r="CB31" s="15"/>
       <c r="CC31" s="3"/>
       <c r="CD31" s="3"/>
       <c r="CE31" s="3"/>
       <c r="CF31" s="3"/>
-      <c r="CG31" s="23"/>
+      <c r="CG31" s="28"/>
       <c r="CH31" s="3"/>
       <c r="CI31" s="3"/>
       <c r="CJ31" s="6"/>
@@ -4530,7 +5338,7 @@
       <c r="CO31" s="6"/>
       <c r="CP31" s="3"/>
       <c r="CQ31" s="4"/>
-      <c r="CR31" s="13"/>
+      <c r="CR31" s="15"/>
       <c r="CS31" s="3"/>
       <c r="CT31" s="3"/>
       <c r="CU31" s="3"/>
@@ -4541,10 +5349,10 @@
       <c r="CZ31" s="8"/>
       <c r="DA31" s="3"/>
       <c r="DB31" s="3"/>
-      <c r="DC31" s="14"/>
-      <c r="DD31" s="14"/>
-    </row>
-    <row r="32" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC31" s="17"/>
+      <c r="DD31" s="17"/>
+    </row>
+    <row r="32" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -4555,11 +5363,11 @@
       <c r="H32" s="5"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
-      <c r="K32" s="15"/>
+      <c r="K32" s="18"/>
       <c r="L32" s="7"/>
       <c r="M32" s="4"/>
       <c r="N32" s="6"/>
-      <c r="O32" s="21"/>
+      <c r="O32" s="26"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
@@ -4597,23 +5405,23 @@
       <c r="AY32" s="4"/>
       <c r="AZ32" s="3"/>
       <c r="BA32" s="4"/>
-      <c r="BB32" s="22"/>
+      <c r="BB32" s="27"/>
       <c r="BC32" s="3"/>
       <c r="BD32" s="3"/>
       <c r="BE32" s="3"/>
       <c r="BF32" s="3"/>
-      <c r="BG32" s="13"/>
+      <c r="BG32" s="15"/>
       <c r="BH32" s="4"/>
       <c r="BI32" s="3"/>
       <c r="BJ32" s="3"/>
-      <c r="BL32" s="12"/>
-      <c r="BM32" s="12"/>
-      <c r="BN32" s="13"/>
+      <c r="BL32" s="14"/>
+      <c r="BM32" s="14"/>
+      <c r="BN32" s="15"/>
       <c r="BO32" s="3"/>
       <c r="BP32" s="3"/>
-      <c r="BQ32" s="13"/>
+      <c r="BQ32" s="15"/>
       <c r="BR32" s="6"/>
-      <c r="BS32" s="14"/>
+      <c r="BS32" s="17"/>
       <c r="BT32" s="3"/>
       <c r="BU32" s="3"/>
       <c r="BV32" s="3"/>
@@ -4622,12 +5430,12 @@
       <c r="BY32" s="3"/>
       <c r="BZ32" s="3"/>
       <c r="CA32" s="3"/>
-      <c r="CB32" s="13"/>
+      <c r="CB32" s="15"/>
       <c r="CC32" s="3"/>
       <c r="CD32" s="3"/>
       <c r="CE32" s="3"/>
       <c r="CF32" s="3"/>
-      <c r="CG32" s="23"/>
+      <c r="CG32" s="28"/>
       <c r="CH32" s="3"/>
       <c r="CI32" s="3"/>
       <c r="CJ32" s="6"/>
@@ -4638,7 +5446,7 @@
       <c r="CO32" s="6"/>
       <c r="CP32" s="3"/>
       <c r="CQ32" s="4"/>
-      <c r="CR32" s="13"/>
+      <c r="CR32" s="15"/>
       <c r="CS32" s="3"/>
       <c r="CT32" s="3"/>
       <c r="CU32" s="3"/>
@@ -4649,10 +5457,10 @@
       <c r="CZ32" s="8"/>
       <c r="DA32" s="3"/>
       <c r="DB32" s="3"/>
-      <c r="DC32" s="14"/>
-      <c r="DD32" s="14"/>
-    </row>
-    <row r="33" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC32" s="17"/>
+      <c r="DD32" s="17"/>
+    </row>
+    <row r="33" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -4663,11 +5471,11 @@
       <c r="H33" s="5"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
-      <c r="K33" s="15"/>
+      <c r="K33" s="18"/>
       <c r="L33" s="7"/>
       <c r="M33" s="4"/>
       <c r="N33" s="6"/>
-      <c r="O33" s="21"/>
+      <c r="O33" s="26"/>
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
@@ -4705,23 +5513,23 @@
       <c r="AY33" s="4"/>
       <c r="AZ33" s="3"/>
       <c r="BA33" s="4"/>
-      <c r="BB33" s="22"/>
+      <c r="BB33" s="27"/>
       <c r="BC33" s="3"/>
       <c r="BD33" s="3"/>
       <c r="BE33" s="3"/>
       <c r="BF33" s="3"/>
-      <c r="BG33" s="13"/>
+      <c r="BG33" s="15"/>
       <c r="BH33" s="4"/>
       <c r="BI33" s="3"/>
       <c r="BJ33" s="3"/>
-      <c r="BL33" s="12"/>
-      <c r="BM33" s="12"/>
-      <c r="BN33" s="13"/>
+      <c r="BL33" s="14"/>
+      <c r="BM33" s="14"/>
+      <c r="BN33" s="15"/>
       <c r="BO33" s="3"/>
       <c r="BP33" s="3"/>
-      <c r="BQ33" s="13"/>
+      <c r="BQ33" s="15"/>
       <c r="BR33" s="6"/>
-      <c r="BS33" s="14"/>
+      <c r="BS33" s="17"/>
       <c r="BT33" s="3"/>
       <c r="BU33" s="3"/>
       <c r="BV33" s="3"/>
@@ -4730,12 +5538,12 @@
       <c r="BY33" s="3"/>
       <c r="BZ33" s="3"/>
       <c r="CA33" s="3"/>
-      <c r="CB33" s="13"/>
+      <c r="CB33" s="15"/>
       <c r="CC33" s="3"/>
       <c r="CD33" s="3"/>
       <c r="CE33" s="3"/>
       <c r="CF33" s="3"/>
-      <c r="CG33" s="23"/>
+      <c r="CG33" s="28"/>
       <c r="CH33" s="3"/>
       <c r="CI33" s="3"/>
       <c r="CJ33" s="6"/>
@@ -4746,7 +5554,7 @@
       <c r="CO33" s="6"/>
       <c r="CP33" s="3"/>
       <c r="CQ33" s="4"/>
-      <c r="CR33" s="13"/>
+      <c r="CR33" s="15"/>
       <c r="CS33" s="3"/>
       <c r="CT33" s="3"/>
       <c r="CU33" s="3"/>
@@ -4757,10 +5565,10 @@
       <c r="CZ33" s="8"/>
       <c r="DA33" s="3"/>
       <c r="DB33" s="3"/>
-      <c r="DC33" s="14"/>
-      <c r="DD33" s="14"/>
-    </row>
-    <row r="34" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC33" s="17"/>
+      <c r="DD33" s="17"/>
+    </row>
+    <row r="34" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -4771,11 +5579,11 @@
       <c r="H34" s="5"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
-      <c r="K34" s="15"/>
+      <c r="K34" s="18"/>
       <c r="L34" s="7"/>
       <c r="M34" s="4"/>
       <c r="N34" s="6"/>
-      <c r="O34" s="21"/>
+      <c r="O34" s="26"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
@@ -4813,23 +5621,23 @@
       <c r="AY34" s="4"/>
       <c r="AZ34" s="3"/>
       <c r="BA34" s="4"/>
-      <c r="BB34" s="22"/>
+      <c r="BB34" s="27"/>
       <c r="BC34" s="3"/>
       <c r="BD34" s="3"/>
       <c r="BE34" s="3"/>
       <c r="BF34" s="3"/>
-      <c r="BG34" s="13"/>
+      <c r="BG34" s="15"/>
       <c r="BH34" s="4"/>
       <c r="BI34" s="3"/>
       <c r="BJ34" s="3"/>
-      <c r="BL34" s="12"/>
-      <c r="BM34" s="12"/>
-      <c r="BN34" s="13"/>
+      <c r="BL34" s="14"/>
+      <c r="BM34" s="14"/>
+      <c r="BN34" s="15"/>
       <c r="BO34" s="3"/>
       <c r="BP34" s="3"/>
-      <c r="BQ34" s="13"/>
+      <c r="BQ34" s="15"/>
       <c r="BR34" s="6"/>
-      <c r="BS34" s="14"/>
+      <c r="BS34" s="17"/>
       <c r="BT34" s="3"/>
       <c r="BU34" s="3"/>
       <c r="BV34" s="3"/>
@@ -4838,12 +5646,12 @@
       <c r="BY34" s="3"/>
       <c r="BZ34" s="3"/>
       <c r="CA34" s="3"/>
-      <c r="CB34" s="13"/>
+      <c r="CB34" s="15"/>
       <c r="CC34" s="3"/>
       <c r="CD34" s="3"/>
       <c r="CE34" s="3"/>
       <c r="CF34" s="3"/>
-      <c r="CG34" s="23"/>
+      <c r="CG34" s="28"/>
       <c r="CH34" s="3"/>
       <c r="CI34" s="3"/>
       <c r="CJ34" s="6"/>
@@ -4854,7 +5662,7 @@
       <c r="CO34" s="6"/>
       <c r="CP34" s="3"/>
       <c r="CQ34" s="4"/>
-      <c r="CR34" s="13"/>
+      <c r="CR34" s="15"/>
       <c r="CS34" s="3"/>
       <c r="CT34" s="3"/>
       <c r="CU34" s="3"/>
@@ -4865,10 +5673,10 @@
       <c r="CZ34" s="8"/>
       <c r="DA34" s="3"/>
       <c r="DB34" s="3"/>
-      <c r="DC34" s="14"/>
-      <c r="DD34" s="14"/>
-    </row>
-    <row r="35" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC34" s="17"/>
+      <c r="DD34" s="17"/>
+    </row>
+    <row r="35" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -4879,11 +5687,11 @@
       <c r="H35" s="5"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="15"/>
+      <c r="K35" s="18"/>
       <c r="L35" s="7"/>
       <c r="M35" s="4"/>
       <c r="N35" s="6"/>
-      <c r="O35" s="21"/>
+      <c r="O35" s="26"/>
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
@@ -4921,23 +5729,23 @@
       <c r="AY35" s="4"/>
       <c r="AZ35" s="3"/>
       <c r="BA35" s="4"/>
-      <c r="BB35" s="22"/>
+      <c r="BB35" s="27"/>
       <c r="BC35" s="3"/>
       <c r="BD35" s="3"/>
       <c r="BE35" s="3"/>
       <c r="BF35" s="3"/>
-      <c r="BG35" s="13"/>
+      <c r="BG35" s="15"/>
       <c r="BH35" s="4"/>
       <c r="BI35" s="3"/>
       <c r="BJ35" s="3"/>
-      <c r="BL35" s="12"/>
-      <c r="BM35" s="12"/>
-      <c r="BN35" s="13"/>
+      <c r="BL35" s="14"/>
+      <c r="BM35" s="14"/>
+      <c r="BN35" s="15"/>
       <c r="BO35" s="3"/>
       <c r="BP35" s="3"/>
-      <c r="BQ35" s="13"/>
+      <c r="BQ35" s="15"/>
       <c r="BR35" s="6"/>
-      <c r="BS35" s="14"/>
+      <c r="BS35" s="17"/>
       <c r="BT35" s="3"/>
       <c r="BU35" s="3"/>
       <c r="BV35" s="3"/>
@@ -4946,12 +5754,12 @@
       <c r="BY35" s="3"/>
       <c r="BZ35" s="3"/>
       <c r="CA35" s="3"/>
-      <c r="CB35" s="13"/>
+      <c r="CB35" s="15"/>
       <c r="CC35" s="3"/>
       <c r="CD35" s="3"/>
       <c r="CE35" s="3"/>
       <c r="CF35" s="3"/>
-      <c r="CG35" s="23"/>
+      <c r="CG35" s="28"/>
       <c r="CH35" s="3"/>
       <c r="CI35" s="3"/>
       <c r="CJ35" s="6"/>
@@ -4962,7 +5770,7 @@
       <c r="CO35" s="6"/>
       <c r="CP35" s="3"/>
       <c r="CQ35" s="4"/>
-      <c r="CR35" s="13"/>
+      <c r="CR35" s="15"/>
       <c r="CS35" s="3"/>
       <c r="CT35" s="3"/>
       <c r="CU35" s="3"/>
@@ -4973,10 +5781,10 @@
       <c r="CZ35" s="8"/>
       <c r="DA35" s="3"/>
       <c r="DB35" s="3"/>
-      <c r="DC35" s="14"/>
-      <c r="DD35" s="14"/>
-    </row>
-    <row r="36" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC35" s="17"/>
+      <c r="DD35" s="17"/>
+    </row>
+    <row r="36" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -4987,11 +5795,11 @@
       <c r="H36" s="5"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="15"/>
+      <c r="K36" s="18"/>
       <c r="L36" s="7"/>
       <c r="M36" s="4"/>
       <c r="N36" s="6"/>
-      <c r="O36" s="21"/>
+      <c r="O36" s="26"/>
       <c r="P36" s="3"/>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
@@ -5029,23 +5837,23 @@
       <c r="AY36" s="4"/>
       <c r="AZ36" s="3"/>
       <c r="BA36" s="4"/>
-      <c r="BB36" s="22"/>
+      <c r="BB36" s="27"/>
       <c r="BC36" s="3"/>
       <c r="BD36" s="3"/>
       <c r="BE36" s="3"/>
       <c r="BF36" s="3"/>
-      <c r="BG36" s="13"/>
+      <c r="BG36" s="15"/>
       <c r="BH36" s="4"/>
       <c r="BI36" s="3"/>
       <c r="BJ36" s="3"/>
-      <c r="BL36" s="12"/>
-      <c r="BM36" s="12"/>
-      <c r="BN36" s="13"/>
+      <c r="BL36" s="14"/>
+      <c r="BM36" s="14"/>
+      <c r="BN36" s="15"/>
       <c r="BO36" s="3"/>
       <c r="BP36" s="3"/>
-      <c r="BQ36" s="13"/>
+      <c r="BQ36" s="15"/>
       <c r="BR36" s="6"/>
-      <c r="BS36" s="14"/>
+      <c r="BS36" s="17"/>
       <c r="BT36" s="3"/>
       <c r="BU36" s="3"/>
       <c r="BV36" s="3"/>
@@ -5054,12 +5862,12 @@
       <c r="BY36" s="3"/>
       <c r="BZ36" s="3"/>
       <c r="CA36" s="3"/>
-      <c r="CB36" s="13"/>
+      <c r="CB36" s="15"/>
       <c r="CC36" s="3"/>
       <c r="CD36" s="3"/>
       <c r="CE36" s="3"/>
       <c r="CF36" s="3"/>
-      <c r="CG36" s="23"/>
+      <c r="CG36" s="28"/>
       <c r="CH36" s="3"/>
       <c r="CI36" s="3"/>
       <c r="CJ36" s="6"/>
@@ -5070,7 +5878,7 @@
       <c r="CO36" s="6"/>
       <c r="CP36" s="3"/>
       <c r="CQ36" s="4"/>
-      <c r="CR36" s="13"/>
+      <c r="CR36" s="15"/>
       <c r="CS36" s="3"/>
       <c r="CT36" s="3"/>
       <c r="CU36" s="3"/>
@@ -5081,10 +5889,10 @@
       <c r="CZ36" s="8"/>
       <c r="DA36" s="3"/>
       <c r="DB36" s="3"/>
-      <c r="DC36" s="14"/>
-      <c r="DD36" s="14"/>
-    </row>
-    <row r="37" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC36" s="17"/>
+      <c r="DD36" s="17"/>
+    </row>
+    <row r="37" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -5095,11 +5903,11 @@
       <c r="H37" s="5"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
-      <c r="K37" s="15"/>
+      <c r="K37" s="18"/>
       <c r="L37" s="7"/>
       <c r="M37" s="4"/>
       <c r="N37" s="6"/>
-      <c r="O37" s="21"/>
+      <c r="O37" s="26"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -5137,23 +5945,23 @@
       <c r="AY37" s="4"/>
       <c r="AZ37" s="3"/>
       <c r="BA37" s="4"/>
-      <c r="BB37" s="22"/>
+      <c r="BB37" s="27"/>
       <c r="BC37" s="3"/>
       <c r="BD37" s="3"/>
       <c r="BE37" s="3"/>
       <c r="BF37" s="3"/>
-      <c r="BG37" s="13"/>
+      <c r="BG37" s="15"/>
       <c r="BH37" s="4"/>
       <c r="BI37" s="3"/>
       <c r="BJ37" s="3"/>
-      <c r="BL37" s="12"/>
-      <c r="BM37" s="12"/>
-      <c r="BN37" s="13"/>
+      <c r="BL37" s="14"/>
+      <c r="BM37" s="14"/>
+      <c r="BN37" s="15"/>
       <c r="BO37" s="3"/>
       <c r="BP37" s="3"/>
-      <c r="BQ37" s="13"/>
+      <c r="BQ37" s="15"/>
       <c r="BR37" s="6"/>
-      <c r="BS37" s="14"/>
+      <c r="BS37" s="17"/>
       <c r="BT37" s="3"/>
       <c r="BU37" s="3"/>
       <c r="BV37" s="3"/>
@@ -5162,12 +5970,12 @@
       <c r="BY37" s="3"/>
       <c r="BZ37" s="3"/>
       <c r="CA37" s="3"/>
-      <c r="CB37" s="13"/>
+      <c r="CB37" s="15"/>
       <c r="CC37" s="3"/>
       <c r="CD37" s="3"/>
       <c r="CE37" s="3"/>
       <c r="CF37" s="3"/>
-      <c r="CG37" s="23"/>
+      <c r="CG37" s="28"/>
       <c r="CH37" s="3"/>
       <c r="CI37" s="3"/>
       <c r="CJ37" s="6"/>
@@ -5178,7 +5986,7 @@
       <c r="CO37" s="6"/>
       <c r="CP37" s="3"/>
       <c r="CQ37" s="4"/>
-      <c r="CR37" s="13"/>
+      <c r="CR37" s="15"/>
       <c r="CS37" s="3"/>
       <c r="CT37" s="3"/>
       <c r="CU37" s="3"/>
@@ -5189,10 +5997,10 @@
       <c r="CZ37" s="8"/>
       <c r="DA37" s="3"/>
       <c r="DB37" s="3"/>
-      <c r="DC37" s="14"/>
-      <c r="DD37" s="14"/>
-    </row>
-    <row r="38" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC37" s="17"/>
+      <c r="DD37" s="17"/>
+    </row>
+    <row r="38" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -5203,11 +6011,11 @@
       <c r="H38" s="5"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
-      <c r="K38" s="15"/>
+      <c r="K38" s="18"/>
       <c r="L38" s="7"/>
       <c r="M38" s="4"/>
       <c r="N38" s="6"/>
-      <c r="O38" s="21"/>
+      <c r="O38" s="26"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -5245,23 +6053,23 @@
       <c r="AY38" s="4"/>
       <c r="AZ38" s="3"/>
       <c r="BA38" s="4"/>
-      <c r="BB38" s="22"/>
+      <c r="BB38" s="27"/>
       <c r="BC38" s="3"/>
       <c r="BD38" s="3"/>
       <c r="BE38" s="3"/>
       <c r="BF38" s="3"/>
-      <c r="BG38" s="13"/>
+      <c r="BG38" s="15"/>
       <c r="BH38" s="4"/>
       <c r="BI38" s="3"/>
       <c r="BJ38" s="3"/>
-      <c r="BL38" s="12"/>
-      <c r="BM38" s="12"/>
-      <c r="BN38" s="13"/>
+      <c r="BL38" s="14"/>
+      <c r="BM38" s="14"/>
+      <c r="BN38" s="15"/>
       <c r="BO38" s="3"/>
       <c r="BP38" s="3"/>
-      <c r="BQ38" s="13"/>
+      <c r="BQ38" s="15"/>
       <c r="BR38" s="6"/>
-      <c r="BS38" s="14"/>
+      <c r="BS38" s="17"/>
       <c r="BT38" s="3"/>
       <c r="BU38" s="3"/>
       <c r="BV38" s="3"/>
@@ -5270,12 +6078,12 @@
       <c r="BY38" s="3"/>
       <c r="BZ38" s="3"/>
       <c r="CA38" s="3"/>
-      <c r="CB38" s="13"/>
+      <c r="CB38" s="15"/>
       <c r="CC38" s="3"/>
       <c r="CD38" s="3"/>
       <c r="CE38" s="3"/>
       <c r="CF38" s="3"/>
-      <c r="CG38" s="23"/>
+      <c r="CG38" s="28"/>
       <c r="CH38" s="3"/>
       <c r="CI38" s="3"/>
       <c r="CJ38" s="6"/>
@@ -5286,7 +6094,7 @@
       <c r="CO38" s="6"/>
       <c r="CP38" s="3"/>
       <c r="CQ38" s="4"/>
-      <c r="CR38" s="13"/>
+      <c r="CR38" s="15"/>
       <c r="CS38" s="3"/>
       <c r="CT38" s="3"/>
       <c r="CU38" s="3"/>
@@ -5297,10 +6105,10 @@
       <c r="CZ38" s="8"/>
       <c r="DA38" s="3"/>
       <c r="DB38" s="3"/>
-      <c r="DC38" s="14"/>
-      <c r="DD38" s="14"/>
-    </row>
-    <row r="39" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC38" s="17"/>
+      <c r="DD38" s="17"/>
+    </row>
+    <row r="39" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -5311,11 +6119,11 @@
       <c r="H39" s="5"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="15"/>
+      <c r="K39" s="18"/>
       <c r="L39" s="7"/>
       <c r="M39" s="4"/>
       <c r="N39" s="6"/>
-      <c r="O39" s="21"/>
+      <c r="O39" s="26"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
@@ -5353,23 +6161,23 @@
       <c r="AY39" s="4"/>
       <c r="AZ39" s="3"/>
       <c r="BA39" s="4"/>
-      <c r="BB39" s="22"/>
+      <c r="BB39" s="27"/>
       <c r="BC39" s="3"/>
       <c r="BD39" s="3"/>
       <c r="BE39" s="3"/>
       <c r="BF39" s="3"/>
-      <c r="BG39" s="13"/>
+      <c r="BG39" s="15"/>
       <c r="BH39" s="4"/>
       <c r="BI39" s="3"/>
       <c r="BJ39" s="3"/>
-      <c r="BL39" s="12"/>
-      <c r="BM39" s="12"/>
-      <c r="BN39" s="13"/>
+      <c r="BL39" s="14"/>
+      <c r="BM39" s="14"/>
+      <c r="BN39" s="15"/>
       <c r="BO39" s="3"/>
       <c r="BP39" s="3"/>
-      <c r="BQ39" s="13"/>
+      <c r="BQ39" s="15"/>
       <c r="BR39" s="6"/>
-      <c r="BS39" s="14"/>
+      <c r="BS39" s="17"/>
       <c r="BT39" s="3"/>
       <c r="BU39" s="3"/>
       <c r="BV39" s="3"/>
@@ -5378,12 +6186,12 @@
       <c r="BY39" s="3"/>
       <c r="BZ39" s="3"/>
       <c r="CA39" s="3"/>
-      <c r="CB39" s="13"/>
+      <c r="CB39" s="15"/>
       <c r="CC39" s="3"/>
       <c r="CD39" s="3"/>
       <c r="CE39" s="3"/>
       <c r="CF39" s="3"/>
-      <c r="CG39" s="23"/>
+      <c r="CG39" s="28"/>
       <c r="CH39" s="3"/>
       <c r="CI39" s="3"/>
       <c r="CJ39" s="6"/>
@@ -5394,7 +6202,7 @@
       <c r="CO39" s="6"/>
       <c r="CP39" s="3"/>
       <c r="CQ39" s="4"/>
-      <c r="CR39" s="13"/>
+      <c r="CR39" s="15"/>
       <c r="CS39" s="3"/>
       <c r="CT39" s="3"/>
       <c r="CU39" s="3"/>
@@ -5405,10 +6213,10 @@
       <c r="CZ39" s="8"/>
       <c r="DA39" s="3"/>
       <c r="DB39" s="3"/>
-      <c r="DC39" s="14"/>
-      <c r="DD39" s="14"/>
-    </row>
-    <row r="40" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC39" s="17"/>
+      <c r="DD39" s="17"/>
+    </row>
+    <row r="40" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -5419,11 +6227,11 @@
       <c r="H40" s="5"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="15"/>
+      <c r="K40" s="18"/>
       <c r="L40" s="7"/>
       <c r="M40" s="4"/>
       <c r="N40" s="6"/>
-      <c r="O40" s="21"/>
+      <c r="O40" s="26"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
@@ -5461,23 +6269,23 @@
       <c r="AY40" s="4"/>
       <c r="AZ40" s="3"/>
       <c r="BA40" s="4"/>
-      <c r="BB40" s="22"/>
+      <c r="BB40" s="27"/>
       <c r="BC40" s="3"/>
       <c r="BD40" s="3"/>
       <c r="BE40" s="3"/>
       <c r="BF40" s="3"/>
-      <c r="BG40" s="13"/>
+      <c r="BG40" s="15"/>
       <c r="BH40" s="4"/>
       <c r="BI40" s="3"/>
       <c r="BJ40" s="3"/>
-      <c r="BL40" s="12"/>
-      <c r="BM40" s="12"/>
-      <c r="BN40" s="13"/>
+      <c r="BL40" s="14"/>
+      <c r="BM40" s="14"/>
+      <c r="BN40" s="15"/>
       <c r="BO40" s="3"/>
       <c r="BP40" s="3"/>
-      <c r="BQ40" s="13"/>
+      <c r="BQ40" s="15"/>
       <c r="BR40" s="6"/>
-      <c r="BS40" s="14"/>
+      <c r="BS40" s="17"/>
       <c r="BT40" s="3"/>
       <c r="BU40" s="3"/>
       <c r="BV40" s="3"/>
@@ -5486,12 +6294,12 @@
       <c r="BY40" s="3"/>
       <c r="BZ40" s="3"/>
       <c r="CA40" s="3"/>
-      <c r="CB40" s="13"/>
+      <c r="CB40" s="15"/>
       <c r="CC40" s="3"/>
       <c r="CD40" s="3"/>
       <c r="CE40" s="3"/>
       <c r="CF40" s="3"/>
-      <c r="CG40" s="23"/>
+      <c r="CG40" s="28"/>
       <c r="CH40" s="3"/>
       <c r="CI40" s="3"/>
       <c r="CJ40" s="6"/>
@@ -5502,7 +6310,7 @@
       <c r="CO40" s="6"/>
       <c r="CP40" s="3"/>
       <c r="CQ40" s="4"/>
-      <c r="CR40" s="13"/>
+      <c r="CR40" s="15"/>
       <c r="CS40" s="3"/>
       <c r="CT40" s="3"/>
       <c r="CU40" s="3"/>
@@ -5513,10 +6321,10 @@
       <c r="CZ40" s="8"/>
       <c r="DA40" s="3"/>
       <c r="DB40" s="3"/>
-      <c r="DC40" s="14"/>
-      <c r="DD40" s="14"/>
-    </row>
-    <row r="41" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC40" s="17"/>
+      <c r="DD40" s="17"/>
+    </row>
+    <row r="41" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -5527,11 +6335,11 @@
       <c r="H41" s="5"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="15"/>
+      <c r="K41" s="18"/>
       <c r="L41" s="7"/>
       <c r="M41" s="4"/>
       <c r="N41" s="6"/>
-      <c r="O41" s="21"/>
+      <c r="O41" s="26"/>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
@@ -5569,23 +6377,23 @@
       <c r="AY41" s="4"/>
       <c r="AZ41" s="3"/>
       <c r="BA41" s="4"/>
-      <c r="BB41" s="22"/>
+      <c r="BB41" s="27"/>
       <c r="BC41" s="3"/>
       <c r="BD41" s="3"/>
       <c r="BE41" s="3"/>
       <c r="BF41" s="3"/>
-      <c r="BG41" s="13"/>
+      <c r="BG41" s="15"/>
       <c r="BH41" s="4"/>
       <c r="BI41" s="3"/>
       <c r="BJ41" s="3"/>
-      <c r="BL41" s="12"/>
-      <c r="BM41" s="12"/>
-      <c r="BN41" s="13"/>
+      <c r="BL41" s="14"/>
+      <c r="BM41" s="14"/>
+      <c r="BN41" s="15"/>
       <c r="BO41" s="3"/>
       <c r="BP41" s="3"/>
-      <c r="BQ41" s="13"/>
+      <c r="BQ41" s="15"/>
       <c r="BR41" s="6"/>
-      <c r="BS41" s="14"/>
+      <c r="BS41" s="17"/>
       <c r="BT41" s="3"/>
       <c r="BU41" s="3"/>
       <c r="BV41" s="3"/>
@@ -5594,12 +6402,12 @@
       <c r="BY41" s="3"/>
       <c r="BZ41" s="3"/>
       <c r="CA41" s="3"/>
-      <c r="CB41" s="13"/>
+      <c r="CB41" s="15"/>
       <c r="CC41" s="3"/>
       <c r="CD41" s="3"/>
       <c r="CE41" s="3"/>
       <c r="CF41" s="3"/>
-      <c r="CG41" s="23"/>
+      <c r="CG41" s="28"/>
       <c r="CH41" s="3"/>
       <c r="CI41" s="3"/>
       <c r="CJ41" s="6"/>
@@ -5610,7 +6418,7 @@
       <c r="CO41" s="6"/>
       <c r="CP41" s="3"/>
       <c r="CQ41" s="4"/>
-      <c r="CR41" s="13"/>
+      <c r="CR41" s="15"/>
       <c r="CS41" s="3"/>
       <c r="CT41" s="3"/>
       <c r="CU41" s="3"/>
@@ -5621,10 +6429,10 @@
       <c r="CZ41" s="8"/>
       <c r="DA41" s="3"/>
       <c r="DB41" s="3"/>
-      <c r="DC41" s="14"/>
-      <c r="DD41" s="14"/>
-    </row>
-    <row r="42" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC41" s="17"/>
+      <c r="DD41" s="17"/>
+    </row>
+    <row r="42" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -5635,11 +6443,11 @@
       <c r="H42" s="5"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
-      <c r="K42" s="15"/>
+      <c r="K42" s="18"/>
       <c r="L42" s="7"/>
       <c r="M42" s="4"/>
       <c r="N42" s="6"/>
-      <c r="O42" s="21"/>
+      <c r="O42" s="26"/>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
       <c r="R42" s="3"/>
@@ -5677,23 +6485,23 @@
       <c r="AY42" s="4"/>
       <c r="AZ42" s="3"/>
       <c r="BA42" s="4"/>
-      <c r="BB42" s="22"/>
+      <c r="BB42" s="27"/>
       <c r="BC42" s="3"/>
       <c r="BD42" s="3"/>
       <c r="BE42" s="3"/>
       <c r="BF42" s="3"/>
-      <c r="BG42" s="13"/>
+      <c r="BG42" s="15"/>
       <c r="BH42" s="4"/>
       <c r="BI42" s="3"/>
       <c r="BJ42" s="3"/>
-      <c r="BL42" s="12"/>
-      <c r="BM42" s="12"/>
-      <c r="BN42" s="13"/>
+      <c r="BL42" s="14"/>
+      <c r="BM42" s="14"/>
+      <c r="BN42" s="15"/>
       <c r="BO42" s="3"/>
       <c r="BP42" s="3"/>
-      <c r="BQ42" s="13"/>
+      <c r="BQ42" s="15"/>
       <c r="BR42" s="6"/>
-      <c r="BS42" s="14"/>
+      <c r="BS42" s="17"/>
       <c r="BT42" s="3"/>
       <c r="BU42" s="3"/>
       <c r="BV42" s="3"/>
@@ -5702,12 +6510,12 @@
       <c r="BY42" s="3"/>
       <c r="BZ42" s="3"/>
       <c r="CA42" s="3"/>
-      <c r="CB42" s="13"/>
+      <c r="CB42" s="15"/>
       <c r="CC42" s="3"/>
       <c r="CD42" s="3"/>
       <c r="CE42" s="3"/>
       <c r="CF42" s="3"/>
-      <c r="CG42" s="23"/>
+      <c r="CG42" s="28"/>
       <c r="CH42" s="3"/>
       <c r="CI42" s="3"/>
       <c r="CJ42" s="6"/>
@@ -5718,7 +6526,7 @@
       <c r="CO42" s="6"/>
       <c r="CP42" s="3"/>
       <c r="CQ42" s="4"/>
-      <c r="CR42" s="13"/>
+      <c r="CR42" s="15"/>
       <c r="CS42" s="3"/>
       <c r="CT42" s="3"/>
       <c r="CU42" s="3"/>
@@ -5729,10 +6537,10 @@
       <c r="CZ42" s="8"/>
       <c r="DA42" s="3"/>
       <c r="DB42" s="3"/>
-      <c r="DC42" s="14"/>
-      <c r="DD42" s="14"/>
-    </row>
-    <row r="43" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC42" s="17"/>
+      <c r="DD42" s="17"/>
+    </row>
+    <row r="43" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -5743,11 +6551,11 @@
       <c r="H43" s="5"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
-      <c r="K43" s="15"/>
+      <c r="K43" s="18"/>
       <c r="L43" s="7"/>
       <c r="M43" s="4"/>
       <c r="N43" s="6"/>
-      <c r="O43" s="21"/>
+      <c r="O43" s="26"/>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
@@ -5785,23 +6593,23 @@
       <c r="AY43" s="4"/>
       <c r="AZ43" s="3"/>
       <c r="BA43" s="4"/>
-      <c r="BB43" s="22"/>
+      <c r="BB43" s="27"/>
       <c r="BC43" s="3"/>
       <c r="BD43" s="3"/>
       <c r="BE43" s="3"/>
       <c r="BF43" s="3"/>
-      <c r="BG43" s="13"/>
+      <c r="BG43" s="15"/>
       <c r="BH43" s="4"/>
       <c r="BI43" s="3"/>
       <c r="BJ43" s="3"/>
-      <c r="BL43" s="12"/>
-      <c r="BM43" s="12"/>
-      <c r="BN43" s="13"/>
+      <c r="BL43" s="14"/>
+      <c r="BM43" s="14"/>
+      <c r="BN43" s="15"/>
       <c r="BO43" s="3"/>
       <c r="BP43" s="3"/>
-      <c r="BQ43" s="13"/>
+      <c r="BQ43" s="15"/>
       <c r="BR43" s="6"/>
-      <c r="BS43" s="14"/>
+      <c r="BS43" s="17"/>
       <c r="BT43" s="3"/>
       <c r="BU43" s="3"/>
       <c r="BV43" s="3"/>
@@ -5810,12 +6618,12 @@
       <c r="BY43" s="3"/>
       <c r="BZ43" s="3"/>
       <c r="CA43" s="3"/>
-      <c r="CB43" s="13"/>
+      <c r="CB43" s="15"/>
       <c r="CC43" s="3"/>
       <c r="CD43" s="3"/>
       <c r="CE43" s="3"/>
       <c r="CF43" s="3"/>
-      <c r="CG43" s="23"/>
+      <c r="CG43" s="28"/>
       <c r="CH43" s="3"/>
       <c r="CI43" s="3"/>
       <c r="CJ43" s="6"/>
@@ -5826,7 +6634,7 @@
       <c r="CO43" s="6"/>
       <c r="CP43" s="3"/>
       <c r="CQ43" s="4"/>
-      <c r="CR43" s="13"/>
+      <c r="CR43" s="15"/>
       <c r="CS43" s="3"/>
       <c r="CT43" s="3"/>
       <c r="CU43" s="3"/>
@@ -5837,10 +6645,10 @@
       <c r="CZ43" s="8"/>
       <c r="DA43" s="3"/>
       <c r="DB43" s="3"/>
-      <c r="DC43" s="14"/>
-      <c r="DD43" s="14"/>
-    </row>
-    <row r="44" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC43" s="17"/>
+      <c r="DD43" s="17"/>
+    </row>
+    <row r="44" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -5851,11 +6659,11 @@
       <c r="H44" s="5"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
-      <c r="K44" s="15"/>
+      <c r="K44" s="18"/>
       <c r="L44" s="7"/>
       <c r="M44" s="4"/>
       <c r="N44" s="6"/>
-      <c r="O44" s="21"/>
+      <c r="O44" s="26"/>
       <c r="P44" s="3"/>
       <c r="Q44" s="3"/>
       <c r="R44" s="3"/>
@@ -5893,23 +6701,23 @@
       <c r="AY44" s="4"/>
       <c r="AZ44" s="3"/>
       <c r="BA44" s="4"/>
-      <c r="BB44" s="22"/>
+      <c r="BB44" s="27"/>
       <c r="BC44" s="3"/>
       <c r="BD44" s="3"/>
       <c r="BE44" s="3"/>
       <c r="BF44" s="3"/>
-      <c r="BG44" s="13"/>
+      <c r="BG44" s="15"/>
       <c r="BH44" s="4"/>
       <c r="BI44" s="3"/>
       <c r="BJ44" s="3"/>
-      <c r="BL44" s="12"/>
-      <c r="BM44" s="12"/>
-      <c r="BN44" s="13"/>
+      <c r="BL44" s="14"/>
+      <c r="BM44" s="14"/>
+      <c r="BN44" s="15"/>
       <c r="BO44" s="3"/>
       <c r="BP44" s="3"/>
-      <c r="BQ44" s="13"/>
+      <c r="BQ44" s="15"/>
       <c r="BR44" s="6"/>
-      <c r="BS44" s="14"/>
+      <c r="BS44" s="17"/>
       <c r="BT44" s="3"/>
       <c r="BU44" s="3"/>
       <c r="BV44" s="3"/>
@@ -5918,12 +6726,12 @@
       <c r="BY44" s="3"/>
       <c r="BZ44" s="3"/>
       <c r="CA44" s="3"/>
-      <c r="CB44" s="13"/>
+      <c r="CB44" s="15"/>
       <c r="CC44" s="3"/>
       <c r="CD44" s="3"/>
       <c r="CE44" s="3"/>
       <c r="CF44" s="3"/>
-      <c r="CG44" s="23"/>
+      <c r="CG44" s="28"/>
       <c r="CH44" s="3"/>
       <c r="CI44" s="3"/>
       <c r="CJ44" s="6"/>
@@ -5934,7 +6742,7 @@
       <c r="CO44" s="6"/>
       <c r="CP44" s="3"/>
       <c r="CQ44" s="4"/>
-      <c r="CR44" s="13"/>
+      <c r="CR44" s="15"/>
       <c r="CS44" s="3"/>
       <c r="CT44" s="3"/>
       <c r="CU44" s="3"/>
@@ -5945,10 +6753,10 @@
       <c r="CZ44" s="8"/>
       <c r="DA44" s="3"/>
       <c r="DB44" s="3"/>
-      <c r="DC44" s="14"/>
-      <c r="DD44" s="14"/>
-    </row>
-    <row r="45" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC44" s="17"/>
+      <c r="DD44" s="17"/>
+    </row>
+    <row r="45" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -5959,11 +6767,11 @@
       <c r="H45" s="5"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
-      <c r="K45" s="15"/>
+      <c r="K45" s="18"/>
       <c r="L45" s="7"/>
       <c r="M45" s="4"/>
       <c r="N45" s="6"/>
-      <c r="O45" s="21"/>
+      <c r="O45" s="26"/>
       <c r="P45" s="3"/>
       <c r="Q45" s="3"/>
       <c r="R45" s="3"/>
@@ -6001,23 +6809,23 @@
       <c r="AY45" s="4"/>
       <c r="AZ45" s="3"/>
       <c r="BA45" s="4"/>
-      <c r="BB45" s="22"/>
+      <c r="BB45" s="27"/>
       <c r="BC45" s="3"/>
       <c r="BD45" s="3"/>
       <c r="BE45" s="3"/>
       <c r="BF45" s="3"/>
-      <c r="BG45" s="13"/>
+      <c r="BG45" s="15"/>
       <c r="BH45" s="4"/>
       <c r="BI45" s="3"/>
       <c r="BJ45" s="3"/>
-      <c r="BL45" s="12"/>
-      <c r="BM45" s="12"/>
-      <c r="BN45" s="13"/>
+      <c r="BL45" s="14"/>
+      <c r="BM45" s="14"/>
+      <c r="BN45" s="15"/>
       <c r="BO45" s="3"/>
       <c r="BP45" s="3"/>
-      <c r="BQ45" s="13"/>
+      <c r="BQ45" s="15"/>
       <c r="BR45" s="6"/>
-      <c r="BS45" s="14"/>
+      <c r="BS45" s="17"/>
       <c r="BT45" s="3"/>
       <c r="BU45" s="3"/>
       <c r="BV45" s="3"/>
@@ -6026,12 +6834,12 @@
       <c r="BY45" s="3"/>
       <c r="BZ45" s="3"/>
       <c r="CA45" s="3"/>
-      <c r="CB45" s="13"/>
+      <c r="CB45" s="15"/>
       <c r="CC45" s="3"/>
       <c r="CD45" s="3"/>
       <c r="CE45" s="3"/>
       <c r="CF45" s="3"/>
-      <c r="CG45" s="23"/>
+      <c r="CG45" s="28"/>
       <c r="CH45" s="3"/>
       <c r="CI45" s="3"/>
       <c r="CJ45" s="6"/>
@@ -6042,7 +6850,7 @@
       <c r="CO45" s="6"/>
       <c r="CP45" s="3"/>
       <c r="CQ45" s="4"/>
-      <c r="CR45" s="13"/>
+      <c r="CR45" s="15"/>
       <c r="CS45" s="3"/>
       <c r="CT45" s="3"/>
       <c r="CU45" s="3"/>
@@ -6053,10 +6861,10 @@
       <c r="CZ45" s="8"/>
       <c r="DA45" s="3"/>
       <c r="DB45" s="3"/>
-      <c r="DC45" s="14"/>
-      <c r="DD45" s="14"/>
-    </row>
-    <row r="46" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC45" s="17"/>
+      <c r="DD45" s="17"/>
+    </row>
+    <row r="46" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -6067,11 +6875,11 @@
       <c r="H46" s="5"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
-      <c r="K46" s="15"/>
+      <c r="K46" s="18"/>
       <c r="L46" s="7"/>
       <c r="M46" s="4"/>
       <c r="N46" s="6"/>
-      <c r="O46" s="21"/>
+      <c r="O46" s="26"/>
       <c r="P46" s="3"/>
       <c r="Q46" s="3"/>
       <c r="R46" s="3"/>
@@ -6109,23 +6917,23 @@
       <c r="AY46" s="4"/>
       <c r="AZ46" s="3"/>
       <c r="BA46" s="4"/>
-      <c r="BB46" s="22"/>
+      <c r="BB46" s="27"/>
       <c r="BC46" s="3"/>
       <c r="BD46" s="3"/>
       <c r="BE46" s="3"/>
       <c r="BF46" s="3"/>
-      <c r="BG46" s="13"/>
+      <c r="BG46" s="15"/>
       <c r="BH46" s="4"/>
       <c r="BI46" s="3"/>
       <c r="BJ46" s="3"/>
-      <c r="BL46" s="12"/>
-      <c r="BM46" s="12"/>
-      <c r="BN46" s="13"/>
+      <c r="BL46" s="14"/>
+      <c r="BM46" s="14"/>
+      <c r="BN46" s="15"/>
       <c r="BO46" s="3"/>
       <c r="BP46" s="3"/>
-      <c r="BQ46" s="13"/>
+      <c r="BQ46" s="15"/>
       <c r="BR46" s="6"/>
-      <c r="BS46" s="14"/>
+      <c r="BS46" s="17"/>
       <c r="BT46" s="3"/>
       <c r="BU46" s="3"/>
       <c r="BV46" s="3"/>
@@ -6134,12 +6942,12 @@
       <c r="BY46" s="3"/>
       <c r="BZ46" s="3"/>
       <c r="CA46" s="3"/>
-      <c r="CB46" s="13"/>
+      <c r="CB46" s="15"/>
       <c r="CC46" s="3"/>
       <c r="CD46" s="3"/>
       <c r="CE46" s="3"/>
       <c r="CF46" s="3"/>
-      <c r="CG46" s="23"/>
+      <c r="CG46" s="28"/>
       <c r="CH46" s="3"/>
       <c r="CI46" s="3"/>
       <c r="CJ46" s="6"/>
@@ -6150,7 +6958,7 @@
       <c r="CO46" s="6"/>
       <c r="CP46" s="3"/>
       <c r="CQ46" s="4"/>
-      <c r="CR46" s="13"/>
+      <c r="CR46" s="15"/>
       <c r="CS46" s="3"/>
       <c r="CT46" s="3"/>
       <c r="CU46" s="3"/>
@@ -6161,10 +6969,10 @@
       <c r="CZ46" s="8"/>
       <c r="DA46" s="3"/>
       <c r="DB46" s="3"/>
-      <c r="DC46" s="14"/>
-      <c r="DD46" s="14"/>
-    </row>
-    <row r="47" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC46" s="17"/>
+      <c r="DD46" s="17"/>
+    </row>
+    <row r="47" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -6175,11 +6983,11 @@
       <c r="H47" s="5"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
-      <c r="K47" s="15"/>
+      <c r="K47" s="18"/>
       <c r="L47" s="7"/>
       <c r="M47" s="4"/>
       <c r="N47" s="6"/>
-      <c r="O47" s="21"/>
+      <c r="O47" s="26"/>
       <c r="P47" s="3"/>
       <c r="Q47" s="3"/>
       <c r="R47" s="3"/>
@@ -6217,23 +7025,23 @@
       <c r="AY47" s="4"/>
       <c r="AZ47" s="3"/>
       <c r="BA47" s="4"/>
-      <c r="BB47" s="22"/>
+      <c r="BB47" s="27"/>
       <c r="BC47" s="3"/>
       <c r="BD47" s="3"/>
       <c r="BE47" s="3"/>
       <c r="BF47" s="3"/>
-      <c r="BG47" s="13"/>
+      <c r="BG47" s="15"/>
       <c r="BH47" s="4"/>
       <c r="BI47" s="3"/>
       <c r="BJ47" s="3"/>
-      <c r="BL47" s="12"/>
-      <c r="BM47" s="12"/>
-      <c r="BN47" s="13"/>
+      <c r="BL47" s="14"/>
+      <c r="BM47" s="14"/>
+      <c r="BN47" s="15"/>
       <c r="BO47" s="3"/>
       <c r="BP47" s="3"/>
-      <c r="BQ47" s="13"/>
+      <c r="BQ47" s="15"/>
       <c r="BR47" s="6"/>
-      <c r="BS47" s="14"/>
+      <c r="BS47" s="17"/>
       <c r="BT47" s="3"/>
       <c r="BU47" s="3"/>
       <c r="BV47" s="3"/>
@@ -6242,12 +7050,12 @@
       <c r="BY47" s="3"/>
       <c r="BZ47" s="3"/>
       <c r="CA47" s="3"/>
-      <c r="CB47" s="13"/>
+      <c r="CB47" s="15"/>
       <c r="CC47" s="3"/>
       <c r="CD47" s="3"/>
       <c r="CE47" s="3"/>
       <c r="CF47" s="3"/>
-      <c r="CG47" s="23"/>
+      <c r="CG47" s="28"/>
       <c r="CH47" s="3"/>
       <c r="CI47" s="3"/>
       <c r="CJ47" s="6"/>
@@ -6258,7 +7066,7 @@
       <c r="CO47" s="6"/>
       <c r="CP47" s="3"/>
       <c r="CQ47" s="4"/>
-      <c r="CR47" s="13"/>
+      <c r="CR47" s="15"/>
       <c r="CS47" s="3"/>
       <c r="CT47" s="3"/>
       <c r="CU47" s="3"/>
@@ -6269,10 +7077,10 @@
       <c r="CZ47" s="8"/>
       <c r="DA47" s="3"/>
       <c r="DB47" s="3"/>
-      <c r="DC47" s="14"/>
-      <c r="DD47" s="14"/>
-    </row>
-    <row r="48" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC47" s="17"/>
+      <c r="DD47" s="17"/>
+    </row>
+    <row r="48" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -6283,11 +7091,11 @@
       <c r="H48" s="5"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
-      <c r="K48" s="15"/>
+      <c r="K48" s="18"/>
       <c r="L48" s="7"/>
       <c r="M48" s="4"/>
       <c r="N48" s="6"/>
-      <c r="O48" s="21"/>
+      <c r="O48" s="26"/>
       <c r="P48" s="3"/>
       <c r="Q48" s="3"/>
       <c r="R48" s="3"/>
@@ -6325,23 +7133,23 @@
       <c r="AY48" s="4"/>
       <c r="AZ48" s="3"/>
       <c r="BA48" s="4"/>
-      <c r="BB48" s="22"/>
+      <c r="BB48" s="27"/>
       <c r="BC48" s="3"/>
       <c r="BD48" s="3"/>
       <c r="BE48" s="3"/>
       <c r="BF48" s="3"/>
-      <c r="BG48" s="13"/>
+      <c r="BG48" s="15"/>
       <c r="BH48" s="4"/>
       <c r="BI48" s="3"/>
       <c r="BJ48" s="3"/>
-      <c r="BL48" s="12"/>
-      <c r="BM48" s="12"/>
-      <c r="BN48" s="13"/>
+      <c r="BL48" s="14"/>
+      <c r="BM48" s="14"/>
+      <c r="BN48" s="15"/>
       <c r="BO48" s="3"/>
       <c r="BP48" s="3"/>
-      <c r="BQ48" s="13"/>
+      <c r="BQ48" s="15"/>
       <c r="BR48" s="6"/>
-      <c r="BS48" s="14"/>
+      <c r="BS48" s="17"/>
       <c r="BT48" s="3"/>
       <c r="BU48" s="3"/>
       <c r="BV48" s="3"/>
@@ -6350,12 +7158,12 @@
       <c r="BY48" s="3"/>
       <c r="BZ48" s="3"/>
       <c r="CA48" s="3"/>
-      <c r="CB48" s="13"/>
+      <c r="CB48" s="15"/>
       <c r="CC48" s="3"/>
       <c r="CD48" s="3"/>
       <c r="CE48" s="3"/>
       <c r="CF48" s="3"/>
-      <c r="CG48" s="23"/>
+      <c r="CG48" s="28"/>
       <c r="CH48" s="3"/>
       <c r="CI48" s="3"/>
       <c r="CJ48" s="6"/>
@@ -6366,7 +7174,7 @@
       <c r="CO48" s="6"/>
       <c r="CP48" s="3"/>
       <c r="CQ48" s="4"/>
-      <c r="CR48" s="13"/>
+      <c r="CR48" s="15"/>
       <c r="CS48" s="3"/>
       <c r="CT48" s="3"/>
       <c r="CU48" s="3"/>
@@ -6377,10 +7185,10 @@
       <c r="CZ48" s="8"/>
       <c r="DA48" s="3"/>
       <c r="DB48" s="3"/>
-      <c r="DC48" s="14"/>
-      <c r="DD48" s="14"/>
-    </row>
-    <row r="49" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC48" s="17"/>
+      <c r="DD48" s="17"/>
+    </row>
+    <row r="49" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -6391,11 +7199,11 @@
       <c r="H49" s="5"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
-      <c r="K49" s="15"/>
+      <c r="K49" s="18"/>
       <c r="L49" s="7"/>
       <c r="M49" s="4"/>
       <c r="N49" s="6"/>
-      <c r="O49" s="21"/>
+      <c r="O49" s="26"/>
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
@@ -6433,23 +7241,23 @@
       <c r="AY49" s="4"/>
       <c r="AZ49" s="3"/>
       <c r="BA49" s="4"/>
-      <c r="BB49" s="22"/>
+      <c r="BB49" s="27"/>
       <c r="BC49" s="3"/>
       <c r="BD49" s="3"/>
       <c r="BE49" s="3"/>
       <c r="BF49" s="3"/>
-      <c r="BG49" s="13"/>
+      <c r="BG49" s="15"/>
       <c r="BH49" s="4"/>
       <c r="BI49" s="3"/>
       <c r="BJ49" s="3"/>
-      <c r="BL49" s="12"/>
-      <c r="BM49" s="12"/>
-      <c r="BN49" s="13"/>
+      <c r="BL49" s="14"/>
+      <c r="BM49" s="14"/>
+      <c r="BN49" s="15"/>
       <c r="BO49" s="3"/>
       <c r="BP49" s="3"/>
-      <c r="BQ49" s="13"/>
+      <c r="BQ49" s="15"/>
       <c r="BR49" s="6"/>
-      <c r="BS49" s="14"/>
+      <c r="BS49" s="17"/>
       <c r="BT49" s="3"/>
       <c r="BU49" s="3"/>
       <c r="BV49" s="3"/>
@@ -6458,12 +7266,12 @@
       <c r="BY49" s="3"/>
       <c r="BZ49" s="3"/>
       <c r="CA49" s="3"/>
-      <c r="CB49" s="13"/>
+      <c r="CB49" s="15"/>
       <c r="CC49" s="3"/>
       <c r="CD49" s="3"/>
       <c r="CE49" s="3"/>
       <c r="CF49" s="3"/>
-      <c r="CG49" s="23"/>
+      <c r="CG49" s="28"/>
       <c r="CH49" s="3"/>
       <c r="CI49" s="3"/>
       <c r="CJ49" s="6"/>
@@ -6474,7 +7282,7 @@
       <c r="CO49" s="6"/>
       <c r="CP49" s="3"/>
       <c r="CQ49" s="4"/>
-      <c r="CR49" s="13"/>
+      <c r="CR49" s="15"/>
       <c r="CS49" s="3"/>
       <c r="CT49" s="3"/>
       <c r="CU49" s="3"/>
@@ -6485,10 +7293,10 @@
       <c r="CZ49" s="8"/>
       <c r="DA49" s="3"/>
       <c r="DB49" s="3"/>
-      <c r="DC49" s="14"/>
-      <c r="DD49" s="14"/>
-    </row>
-    <row r="50" spans="1:108" x14ac:dyDescent="0.25">
+      <c r="DC49" s="17"/>
+      <c r="DD49" s="17"/>
+    </row>
+    <row r="50" spans="1:108" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -6499,11 +7307,11 @@
       <c r="H50" s="5"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
-      <c r="K50" s="15"/>
+      <c r="K50" s="18"/>
       <c r="L50" s="7"/>
       <c r="M50" s="4"/>
       <c r="N50" s="6"/>
-      <c r="O50" s="21"/>
+      <c r="O50" s="26"/>
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
@@ -6541,23 +7349,23 @@
       <c r="AY50" s="4"/>
       <c r="AZ50" s="3"/>
       <c r="BA50" s="4"/>
-      <c r="BB50" s="22"/>
+      <c r="BB50" s="27"/>
       <c r="BC50" s="3"/>
       <c r="BD50" s="3"/>
       <c r="BE50" s="3"/>
       <c r="BF50" s="3"/>
-      <c r="BG50" s="13"/>
+      <c r="BG50" s="15"/>
       <c r="BH50" s="4"/>
       <c r="BI50" s="3"/>
       <c r="BJ50" s="3"/>
-      <c r="BL50" s="12"/>
-      <c r="BM50" s="12"/>
-      <c r="BN50" s="13"/>
+      <c r="BL50" s="14"/>
+      <c r="BM50" s="14"/>
+      <c r="BN50" s="15"/>
       <c r="BO50" s="3"/>
       <c r="BP50" s="3"/>
-      <c r="BQ50" s="13"/>
+      <c r="BQ50" s="15"/>
       <c r="BR50" s="6"/>
-      <c r="BS50" s="14"/>
+      <c r="BS50" s="17"/>
       <c r="BT50" s="3"/>
       <c r="BU50" s="3"/>
       <c r="BV50" s="3"/>
@@ -6566,12 +7374,12 @@
       <c r="BY50" s="3"/>
       <c r="BZ50" s="3"/>
       <c r="CA50" s="3"/>
-      <c r="CB50" s="13"/>
+      <c r="CB50" s="15"/>
       <c r="CC50" s="3"/>
       <c r="CD50" s="3"/>
       <c r="CE50" s="3"/>
       <c r="CF50" s="3"/>
-      <c r="CG50" s="23"/>
+      <c r="CG50" s="28"/>
       <c r="CH50" s="3"/>
       <c r="CI50" s="3"/>
       <c r="CJ50" s="6"/>
@@ -6582,7 +7390,7 @@
       <c r="CO50" s="6"/>
       <c r="CP50" s="3"/>
       <c r="CQ50" s="4"/>
-      <c r="CR50" s="13"/>
+      <c r="CR50" s="15"/>
       <c r="CS50" s="3"/>
       <c r="CT50" s="3"/>
       <c r="CU50" s="3"/>
@@ -6593,8 +7401,8 @@
       <c r="CZ50" s="8"/>
       <c r="DA50" s="3"/>
       <c r="DB50" s="3"/>
-      <c r="DC50" s="14"/>
-      <c r="DD50" s="14"/>
+      <c r="DC50" s="17"/>
+      <c r="DD50" s="17"/>
     </row>
   </sheetData>
   <dataConsolidate/>
@@ -6631,7 +7439,4016 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Hoja3"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B2" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A2,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B3" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A3,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B4" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A4,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B5" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A5,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B6" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A6,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B7" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A7,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B8" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A8,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B9" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A9,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B10" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A10,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B11" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A11,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B12" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A12,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B13" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A13,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B14" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A14,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B15" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A15,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B16" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A16,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A17,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A18,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A19,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A20,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A21,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A22,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A23,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A24,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A25,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B26" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A26,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A27,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B28" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A28,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B29" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A29,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B30" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A30,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A31,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B32" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A32,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B33" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A33,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B34" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A34,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B35" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A35,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B36" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A36,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B37" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A37,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B38" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A38,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B39" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A39,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B40" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A40,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B41" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A41,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B42" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A42,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B43" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A43,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B44" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A44,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B45" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A45,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B46" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A46,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B47" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A47,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B48" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A48,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B49" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A49,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B50" s="10" t="str">
+        <f>IFERROR(VLOOKUP(A50,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C50" xr:uid="{00000000-0002-0000-0300-000000000000}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr codeName="Hoja7"/>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="9"/>
+      <c r="B2" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A2,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C2" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A2,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D2" s="9"/>
+      <c r="E2" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A2,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A2,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I2" s="9"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="9"/>
+      <c r="B3" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A3,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C3" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A3,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A3,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A3,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I3" s="9"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
+      <c r="B4" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A4,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C4" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A4,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A4,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A4,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I4" s="9"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="9"/>
+      <c r="B5" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A5,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C5" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A5,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A5,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A5,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I5" s="9"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="9"/>
+      <c r="B6" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A6,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C6" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A6,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D6" s="9"/>
+      <c r="E6" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A6,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A6,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I6" s="9"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="9"/>
+      <c r="B7" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A7,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C7" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A7,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A7,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A7,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I7" s="9"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A8,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C8" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A8,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A8,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A8,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="9"/>
+      <c r="B9" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A9,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C9" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A9,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A9,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A9,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
+      <c r="B10" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A10,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C10" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A10,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A10,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A10,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="9"/>
+      <c r="B11" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A11,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C11" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A11,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A11,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A11,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="9"/>
+      <c r="B12" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A12,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C12" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A12,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A12,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A12,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="B13" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A13,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C13" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A13,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A13,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A13,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="B14" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A14,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C14" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A14,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A14,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A14,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I14" s="9"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="9"/>
+      <c r="B15" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A15,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C15" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A15,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A15,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A15,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="9"/>
+      <c r="B16" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A16,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C16" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A16,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A16,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A16,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="9"/>
+      <c r="B17" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A17,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C17" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A17,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A17,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A17,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I17" s="9"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="9"/>
+      <c r="B18" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A18,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C18" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A18,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A18,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A18,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I18" s="9"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="9"/>
+      <c r="B19" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A19,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C19" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A19,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A19,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A19,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I19" s="9"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="9"/>
+      <c r="B20" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A20,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C20" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A20,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A20,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A20,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="9"/>
+      <c r="B21" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A21,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C21" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A21,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A21,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A21,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I21" s="9"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="9"/>
+      <c r="B22" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A22,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C22" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A22,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A22,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A22,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I22" s="9"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="9"/>
+      <c r="B23" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A23,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C23" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A23,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A23,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A23,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="9"/>
+      <c r="B24" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A24,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C24" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A24,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A24,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A24,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="9"/>
+      <c r="B25" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A25,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C25" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A25,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A25,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A25,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="9"/>
+      <c r="B26" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A26,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C26" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A26,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D26" s="9"/>
+      <c r="E26" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A26,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A26,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="9"/>
+      <c r="B27" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A27,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C27" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A27,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D27" s="9"/>
+      <c r="E27" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A27,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A27,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="9"/>
+      <c r="B28" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A28,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C28" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A28,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D28" s="9"/>
+      <c r="E28" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A28,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A28,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="9"/>
+      <c r="B29" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A29,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C29" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A29,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D29" s="9"/>
+      <c r="E29" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A29,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A29,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="9"/>
+      <c r="B30" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A30,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C30" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A30,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D30" s="9"/>
+      <c r="E30" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A30,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A30,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I30" s="9"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="9"/>
+      <c r="B31" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A31,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C31" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A31,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D31" s="9"/>
+      <c r="E31" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A31,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A31,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I31" s="9"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="9"/>
+      <c r="B32" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A32,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C32" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A32,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D32" s="9"/>
+      <c r="E32" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A32,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A32,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I32" s="9"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="9"/>
+      <c r="B33" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A33,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C33" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A33,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D33" s="9"/>
+      <c r="E33" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A33,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A33,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I33" s="9"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="9"/>
+      <c r="B34" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A34,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C34" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A34,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D34" s="9"/>
+      <c r="E34" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A34,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A34,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I34" s="9"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="9"/>
+      <c r="B35" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A35,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C35" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A35,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D35" s="9"/>
+      <c r="E35" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A35,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A35,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="9"/>
+      <c r="B36" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A36,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C36" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A36,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D36" s="9"/>
+      <c r="E36" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A36,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A36,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="9"/>
+      <c r="B37" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A37,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C37" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A37,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D37" s="9"/>
+      <c r="E37" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A37,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A37,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I37" s="9"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
+      <c r="B38" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A38,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C38" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A38,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D38" s="9"/>
+      <c r="E38" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A38,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A38,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I38" s="9"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+      <c r="B39" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A39,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C39" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A39,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D39" s="9"/>
+      <c r="E39" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A39,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A39,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I39" s="9"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="9"/>
+      <c r="B40" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A40,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C40" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A40,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D40" s="9"/>
+      <c r="E40" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A40,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A40,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I40" s="9"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
+      <c r="B41" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A41,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C41" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A41,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D41" s="9"/>
+      <c r="E41" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A41,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A41,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I41" s="9"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
+      <c r="B42" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A42,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C42" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A42,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A42,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A42,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I42" s="9"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
+      <c r="B43" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A43,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C43" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A43,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A43,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A43,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I43" s="9"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="B44" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A44,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C44" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A44,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D44" s="9"/>
+      <c r="E44" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A44,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A44,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I44" s="9"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
+      <c r="B45" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A45,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C45" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A45,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D45" s="9"/>
+      <c r="E45" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A45,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A45,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I45" s="9"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="9"/>
+      <c r="B46" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A46,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C46" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A46,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D46" s="9"/>
+      <c r="E46" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A46,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A46,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I46" s="9"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="9"/>
+      <c r="B47" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A47,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C47" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A47,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D47" s="9"/>
+      <c r="E47" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A47,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A47,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I47" s="9"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="9"/>
+      <c r="B48" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A48,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C48" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A48,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D48" s="9"/>
+      <c r="E48" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A48,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A48,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I48" s="9"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="9"/>
+      <c r="B49" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A49,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C49" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A49,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D49" s="9"/>
+      <c r="E49" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A49,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A49,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I49" s="9"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="9"/>
+      <c r="B50" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A50,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C50" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A50,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D50" s="9"/>
+      <c r="E50" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A50,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A50,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I50" s="9"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="9"/>
+      <c r="B51" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A51,#REF!,104,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="C51" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A51,#REF!,44,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="D51" s="9"/>
+      <c r="E51" s="23" t="str">
+        <f>+IFERROR(VLOOKUP(A51,#REF!,69,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="23" t="str">
+        <f>IFERROR(VLOOKUP(A51,#REF!,77,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="I51" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{00000000-0002-0000-0600-000000000000}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCC7BCBD-A269-4128-BBB8-691D0AC5E65D}">
+  <sheetPr codeName="Hoja6"/>
+  <dimension ref="A1:AL50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="45" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A1" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="K1" s="31" t="s">
+        <v>169</v>
+      </c>
+      <c r="L1" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="M1" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="N1" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="O1" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="R1" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="V1" s="16">
+        <v>9904</v>
+      </c>
+      <c r="W1" s="16"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z1" s="32"/>
+      <c r="AA1" s="32"/>
+      <c r="AB1" s="32"/>
+      <c r="AC1" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD1" s="33"/>
+      <c r="AE1" s="33"/>
+      <c r="AF1" s="33"/>
+      <c r="AG1" s="33"/>
+      <c r="AH1" s="33"/>
+      <c r="AI1" s="33"/>
+      <c r="AJ1" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK1" s="35"/>
+      <c r="AL1" s="35"/>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="P2" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q2" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="R2" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="S2" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="U2" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="V2" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="W2" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="X2" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y2" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z2" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA2" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="AB2" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="AC2" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AD2" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="AE2" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF2" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG2" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH2" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="AI2" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="AJ2" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK2" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL2" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A3" s="9"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
+      <c r="Y3" s="9"/>
+      <c r="Z3" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y3,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="9"/>
+      <c r="AF3" s="9"/>
+      <c r="AG3" s="9"/>
+      <c r="AH3" s="9"/>
+      <c r="AI3" s="9"/>
+      <c r="AJ3" s="29"/>
+      <c r="AK3" s="9"/>
+      <c r="AL3" s="9"/>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
+      <c r="Z4" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y4,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="9"/>
+      <c r="AJ4" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK4,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="9"/>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A5" s="9"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y5,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK5,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A6" s="9"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y6,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9"/>
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="9"/>
+      <c r="AJ6" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK6,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A7" s="9"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y7,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AH7" s="9"/>
+      <c r="AI7" s="9"/>
+      <c r="AJ7" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK7,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK7" s="9"/>
+      <c r="AL7" s="9"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="9"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y8,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="9"/>
+      <c r="AJ8" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK8,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A9" s="9"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y9,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="9"/>
+      <c r="AI9" s="9"/>
+      <c r="AJ9" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK9,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK9" s="9"/>
+      <c r="AL9" s="9"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A10" s="9"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+      <c r="Z10" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y10,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9"/>
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="9"/>
+      <c r="AG10" s="9"/>
+      <c r="AH10" s="9"/>
+      <c r="AI10" s="9"/>
+      <c r="AJ10" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK10,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK10" s="9"/>
+      <c r="AL10" s="9"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A11" s="9"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y11,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9"/>
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="9"/>
+      <c r="AH11" s="9"/>
+      <c r="AI11" s="9"/>
+      <c r="AJ11" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK11,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK11" s="9"/>
+      <c r="AL11" s="9"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A12" s="9"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="9"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y12,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="9"/>
+      <c r="AG12" s="9"/>
+      <c r="AH12" s="9"/>
+      <c r="AI12" s="9"/>
+      <c r="AJ12" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK12,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK12" s="9"/>
+      <c r="AL12" s="9"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A13" s="9"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y13,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="9"/>
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK13,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="9"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A14" s="9"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y14,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="9"/>
+      <c r="AF14" s="9"/>
+      <c r="AG14" s="9"/>
+      <c r="AH14" s="9"/>
+      <c r="AI14" s="9"/>
+      <c r="AJ14" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK14,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK14" s="9"/>
+      <c r="AL14" s="9"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A15" s="9"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y15,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="9"/>
+      <c r="AG15" s="9"/>
+      <c r="AH15" s="9"/>
+      <c r="AI15" s="9"/>
+      <c r="AJ15" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK15,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK15" s="9"/>
+      <c r="AL15" s="9"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A16" s="9"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
+      <c r="Z16" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y16,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="9"/>
+      <c r="AE16" s="9"/>
+      <c r="AF16" s="9"/>
+      <c r="AG16" s="9"/>
+      <c r="AH16" s="9"/>
+      <c r="AI16" s="9"/>
+      <c r="AJ16" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK16,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK16" s="9"/>
+      <c r="AL16" s="9"/>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A17" s="9"/>
+      <c r="B17" s="29"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y17,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="9"/>
+      <c r="AF17" s="9"/>
+      <c r="AG17" s="9"/>
+      <c r="AH17" s="9"/>
+      <c r="AI17" s="9"/>
+      <c r="AJ17" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK17,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK17" s="9"/>
+      <c r="AL17" s="9"/>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A18" s="9"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="9"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
+      <c r="Z18" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y18,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="9"/>
+      <c r="AF18" s="9"/>
+      <c r="AG18" s="9"/>
+      <c r="AH18" s="9"/>
+      <c r="AI18" s="9"/>
+      <c r="AJ18" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK18,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK18" s="9"/>
+      <c r="AL18" s="9"/>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A19" s="9"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y19,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="9"/>
+      <c r="AF19" s="9"/>
+      <c r="AG19" s="9"/>
+      <c r="AH19" s="9"/>
+      <c r="AI19" s="9"/>
+      <c r="AJ19" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK19,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK19" s="9"/>
+      <c r="AL19" s="9"/>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A20" s="9"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
+      <c r="S20" s="9"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="9"/>
+      <c r="V20" s="9"/>
+      <c r="W20" s="9"/>
+      <c r="X20" s="9"/>
+      <c r="Y20" s="9"/>
+      <c r="Z20" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y20,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA20" s="9"/>
+      <c r="AB20" s="9"/>
+      <c r="AC20" s="9"/>
+      <c r="AD20" s="9"/>
+      <c r="AE20" s="9"/>
+      <c r="AF20" s="9"/>
+      <c r="AG20" s="9"/>
+      <c r="AH20" s="9"/>
+      <c r="AI20" s="9"/>
+      <c r="AJ20" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK20,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK20" s="9"/>
+      <c r="AL20" s="9"/>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A21" s="9"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y21,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+      <c r="AD21" s="9"/>
+      <c r="AE21" s="9"/>
+      <c r="AF21" s="9"/>
+      <c r="AG21" s="9"/>
+      <c r="AH21" s="9"/>
+      <c r="AI21" s="9"/>
+      <c r="AJ21" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK21,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK21" s="9"/>
+      <c r="AL21" s="9"/>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A22" s="9"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="9"/>
+      <c r="R22" s="9"/>
+      <c r="S22" s="9"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9"/>
+      <c r="V22" s="9"/>
+      <c r="W22" s="9"/>
+      <c r="X22" s="9"/>
+      <c r="Y22" s="9"/>
+      <c r="Z22" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y22,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA22" s="9"/>
+      <c r="AB22" s="9"/>
+      <c r="AC22" s="9"/>
+      <c r="AD22" s="9"/>
+      <c r="AE22" s="9"/>
+      <c r="AF22" s="9"/>
+      <c r="AG22" s="9"/>
+      <c r="AH22" s="9"/>
+      <c r="AI22" s="9"/>
+      <c r="AJ22" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK22,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK22" s="9"/>
+      <c r="AL22" s="9"/>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A23" s="9"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y23,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="9"/>
+      <c r="AG23" s="9"/>
+      <c r="AH23" s="9"/>
+      <c r="AI23" s="9"/>
+      <c r="AJ23" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK23,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK23" s="9"/>
+      <c r="AL23" s="9"/>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A24" s="9"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="9"/>
+      <c r="R24" s="9"/>
+      <c r="S24" s="9"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="9"/>
+      <c r="V24" s="9"/>
+      <c r="W24" s="9"/>
+      <c r="X24" s="9"/>
+      <c r="Y24" s="9"/>
+      <c r="Z24" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y24,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA24" s="9"/>
+      <c r="AB24" s="9"/>
+      <c r="AC24" s="9"/>
+      <c r="AD24" s="9"/>
+      <c r="AE24" s="9"/>
+      <c r="AF24" s="9"/>
+      <c r="AG24" s="9"/>
+      <c r="AH24" s="9"/>
+      <c r="AI24" s="9"/>
+      <c r="AJ24" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK24,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK24" s="9"/>
+      <c r="AL24" s="9"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A25" s="9"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y25,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="9"/>
+      <c r="AF25" s="9"/>
+      <c r="AG25" s="9"/>
+      <c r="AH25" s="9"/>
+      <c r="AI25" s="9"/>
+      <c r="AJ25" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK25,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK25" s="9"/>
+      <c r="AL25" s="9"/>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A26" s="9"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="P26" s="9"/>
+      <c r="Q26" s="9"/>
+      <c r="R26" s="9"/>
+      <c r="S26" s="9"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="9"/>
+      <c r="V26" s="9"/>
+      <c r="W26" s="9"/>
+      <c r="X26" s="9"/>
+      <c r="Y26" s="9"/>
+      <c r="Z26" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y26,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA26" s="9"/>
+      <c r="AB26" s="9"/>
+      <c r="AC26" s="9"/>
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9"/>
+      <c r="AF26" s="9"/>
+      <c r="AG26" s="9"/>
+      <c r="AH26" s="9"/>
+      <c r="AI26" s="9"/>
+      <c r="AJ26" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK26,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK26" s="9"/>
+      <c r="AL26" s="9"/>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A27" s="9"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y27,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+      <c r="AF27" s="9"/>
+      <c r="AG27" s="9"/>
+      <c r="AH27" s="9"/>
+      <c r="AI27" s="9"/>
+      <c r="AJ27" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK27,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK27" s="9"/>
+      <c r="AL27" s="9"/>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A28" s="9"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y28,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA28" s="9"/>
+      <c r="AB28" s="9"/>
+      <c r="AC28" s="9"/>
+      <c r="AD28" s="9"/>
+      <c r="AE28" s="9"/>
+      <c r="AF28" s="9"/>
+      <c r="AG28" s="9"/>
+      <c r="AH28" s="9"/>
+      <c r="AI28" s="9"/>
+      <c r="AJ28" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK28,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK28" s="9"/>
+      <c r="AL28" s="9"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A29" s="9"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y29,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+      <c r="AD29" s="9"/>
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="9"/>
+      <c r="AG29" s="9"/>
+      <c r="AH29" s="9"/>
+      <c r="AI29" s="9"/>
+      <c r="AJ29" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK29,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK29" s="9"/>
+      <c r="AL29" s="9"/>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A30" s="9"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="P30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="R30" s="9"/>
+      <c r="S30" s="9"/>
+      <c r="T30" s="9"/>
+      <c r="U30" s="9"/>
+      <c r="V30" s="9"/>
+      <c r="W30" s="9"/>
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9"/>
+      <c r="Z30" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y30,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA30" s="9"/>
+      <c r="AB30" s="9"/>
+      <c r="AC30" s="9"/>
+      <c r="AD30" s="9"/>
+      <c r="AE30" s="9"/>
+      <c r="AF30" s="9"/>
+      <c r="AG30" s="9"/>
+      <c r="AH30" s="9"/>
+      <c r="AI30" s="9"/>
+      <c r="AJ30" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK30,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK30" s="9"/>
+      <c r="AL30" s="9"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A31" s="9"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y31,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
+      <c r="AD31" s="9"/>
+      <c r="AE31" s="9"/>
+      <c r="AF31" s="9"/>
+      <c r="AG31" s="9"/>
+      <c r="AH31" s="9"/>
+      <c r="AI31" s="9"/>
+      <c r="AJ31" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK31,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK31" s="9"/>
+      <c r="AL31" s="9"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A32" s="9"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+      <c r="M32" s="9"/>
+      <c r="N32" s="9"/>
+      <c r="O32" s="9"/>
+      <c r="P32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="R32" s="9"/>
+      <c r="S32" s="9"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="9"/>
+      <c r="V32" s="9"/>
+      <c r="W32" s="9"/>
+      <c r="X32" s="9"/>
+      <c r="Y32" s="9"/>
+      <c r="Z32" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y32,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA32" s="9"/>
+      <c r="AB32" s="9"/>
+      <c r="AC32" s="9"/>
+      <c r="AD32" s="9"/>
+      <c r="AE32" s="9"/>
+      <c r="AF32" s="9"/>
+      <c r="AG32" s="9"/>
+      <c r="AH32" s="9"/>
+      <c r="AI32" s="9"/>
+      <c r="AJ32" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK32,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK32" s="9"/>
+      <c r="AL32" s="9"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A33" s="9"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y33,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+      <c r="AD33" s="9"/>
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="9"/>
+      <c r="AG33" s="9"/>
+      <c r="AH33" s="9"/>
+      <c r="AI33" s="9"/>
+      <c r="AJ33" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK33,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK33" s="9"/>
+      <c r="AL33" s="9"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A34" s="9"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+      <c r="M34" s="9"/>
+      <c r="N34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="P34" s="9"/>
+      <c r="Q34" s="9"/>
+      <c r="R34" s="9"/>
+      <c r="S34" s="9"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="9"/>
+      <c r="V34" s="9"/>
+      <c r="W34" s="9"/>
+      <c r="X34" s="9"/>
+      <c r="Y34" s="9"/>
+      <c r="Z34" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y34,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA34" s="9"/>
+      <c r="AB34" s="9"/>
+      <c r="AC34" s="9"/>
+      <c r="AD34" s="9"/>
+      <c r="AE34" s="9"/>
+      <c r="AF34" s="9"/>
+      <c r="AG34" s="9"/>
+      <c r="AH34" s="9"/>
+      <c r="AI34" s="9"/>
+      <c r="AJ34" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK34,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK34" s="9"/>
+      <c r="AL34" s="9"/>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A35" s="9"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y35,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
+      <c r="AD35" s="9"/>
+      <c r="AE35" s="9"/>
+      <c r="AF35" s="9"/>
+      <c r="AG35" s="9"/>
+      <c r="AH35" s="9"/>
+      <c r="AI35" s="9"/>
+      <c r="AJ35" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK35,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK35" s="9"/>
+      <c r="AL35" s="9"/>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A36" s="9"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+      <c r="M36" s="9"/>
+      <c r="N36" s="9"/>
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y36,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="9"/>
+      <c r="AC36" s="9"/>
+      <c r="AD36" s="9"/>
+      <c r="AE36" s="9"/>
+      <c r="AF36" s="9"/>
+      <c r="AG36" s="9"/>
+      <c r="AH36" s="9"/>
+      <c r="AI36" s="9"/>
+      <c r="AJ36" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK36,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK36" s="9"/>
+      <c r="AL36" s="9"/>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A37" s="9"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y37,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+      <c r="AE37" s="9"/>
+      <c r="AF37" s="9"/>
+      <c r="AG37" s="9"/>
+      <c r="AH37" s="9"/>
+      <c r="AI37" s="9"/>
+      <c r="AJ37" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK37,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK37" s="9"/>
+      <c r="AL37" s="9"/>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+      <c r="M38" s="9"/>
+      <c r="N38" s="9"/>
+      <c r="O38" s="9"/>
+      <c r="P38" s="9"/>
+      <c r="Q38" s="9"/>
+      <c r="R38" s="9"/>
+      <c r="S38" s="9"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="9"/>
+      <c r="V38" s="9"/>
+      <c r="W38" s="9"/>
+      <c r="X38" s="9"/>
+      <c r="Y38" s="9"/>
+      <c r="Z38" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y38,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA38" s="9"/>
+      <c r="AB38" s="9"/>
+      <c r="AC38" s="9"/>
+      <c r="AD38" s="9"/>
+      <c r="AE38" s="9"/>
+      <c r="AF38" s="9"/>
+      <c r="AG38" s="9"/>
+      <c r="AH38" s="9"/>
+      <c r="AI38" s="9"/>
+      <c r="AJ38" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK38,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK38" s="9"/>
+      <c r="AL38" s="9"/>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y39,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="9"/>
+      <c r="AE39" s="9"/>
+      <c r="AF39" s="9"/>
+      <c r="AG39" s="9"/>
+      <c r="AH39" s="9"/>
+      <c r="AI39" s="9"/>
+      <c r="AJ39" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK39,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK39" s="9"/>
+      <c r="AL39" s="9"/>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A40" s="9"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+      <c r="M40" s="9"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="9"/>
+      <c r="P40" s="9"/>
+      <c r="Q40" s="9"/>
+      <c r="R40" s="9"/>
+      <c r="S40" s="9"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="9"/>
+      <c r="V40" s="9"/>
+      <c r="W40" s="9"/>
+      <c r="X40" s="9"/>
+      <c r="Y40" s="9"/>
+      <c r="Z40" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y40,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA40" s="9"/>
+      <c r="AB40" s="9"/>
+      <c r="AC40" s="9"/>
+      <c r="AD40" s="9"/>
+      <c r="AE40" s="9"/>
+      <c r="AF40" s="9"/>
+      <c r="AG40" s="9"/>
+      <c r="AH40" s="9"/>
+      <c r="AI40" s="9"/>
+      <c r="AJ40" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK40,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK40" s="9"/>
+      <c r="AL40" s="9"/>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A41" s="9"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y41,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="9"/>
+      <c r="AD41" s="9"/>
+      <c r="AE41" s="9"/>
+      <c r="AF41" s="9"/>
+      <c r="AG41" s="9"/>
+      <c r="AH41" s="9"/>
+      <c r="AI41" s="9"/>
+      <c r="AJ41" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK41,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK41" s="9"/>
+      <c r="AL41" s="9"/>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A42" s="9"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+      <c r="M42" s="9"/>
+      <c r="N42" s="9"/>
+      <c r="O42" s="9"/>
+      <c r="P42" s="9"/>
+      <c r="Q42" s="9"/>
+      <c r="R42" s="9"/>
+      <c r="S42" s="9"/>
+      <c r="T42" s="9"/>
+      <c r="U42" s="9"/>
+      <c r="V42" s="9"/>
+      <c r="W42" s="9"/>
+      <c r="X42" s="9"/>
+      <c r="Y42" s="9"/>
+      <c r="Z42" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y42,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA42" s="9"/>
+      <c r="AB42" s="9"/>
+      <c r="AC42" s="9"/>
+      <c r="AD42" s="9"/>
+      <c r="AE42" s="9"/>
+      <c r="AF42" s="9"/>
+      <c r="AG42" s="9"/>
+      <c r="AH42" s="9"/>
+      <c r="AI42" s="9"/>
+      <c r="AJ42" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK42,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK42" s="9"/>
+      <c r="AL42" s="9"/>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A43" s="9"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y43,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA43" s="9"/>
+      <c r="AB43" s="9"/>
+      <c r="AC43" s="9"/>
+      <c r="AD43" s="9"/>
+      <c r="AE43" s="9"/>
+      <c r="AF43" s="9"/>
+      <c r="AG43" s="9"/>
+      <c r="AH43" s="9"/>
+      <c r="AI43" s="9"/>
+      <c r="AJ43" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK43,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK43" s="9"/>
+      <c r="AL43" s="9"/>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+      <c r="M44" s="9"/>
+      <c r="N44" s="9"/>
+      <c r="O44" s="9"/>
+      <c r="P44" s="9"/>
+      <c r="Q44" s="9"/>
+      <c r="R44" s="9"/>
+      <c r="S44" s="9"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="9"/>
+      <c r="V44" s="9"/>
+      <c r="W44" s="9"/>
+      <c r="X44" s="9"/>
+      <c r="Y44" s="9"/>
+      <c r="Z44" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y44,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA44" s="9"/>
+      <c r="AB44" s="9"/>
+      <c r="AC44" s="9"/>
+      <c r="AD44" s="9"/>
+      <c r="AE44" s="9"/>
+      <c r="AF44" s="9"/>
+      <c r="AG44" s="9"/>
+      <c r="AH44" s="9"/>
+      <c r="AI44" s="9"/>
+      <c r="AJ44" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK44,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK44" s="9"/>
+      <c r="AL44" s="9"/>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A45" s="9"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y45,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="9"/>
+      <c r="AC45" s="9"/>
+      <c r="AD45" s="9"/>
+      <c r="AE45" s="9"/>
+      <c r="AF45" s="9"/>
+      <c r="AG45" s="9"/>
+      <c r="AH45" s="9"/>
+      <c r="AI45" s="9"/>
+      <c r="AJ45" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK45,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK45" s="9"/>
+      <c r="AL45" s="9"/>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A46" s="9"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="9"/>
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y46,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="9"/>
+      <c r="AC46" s="9"/>
+      <c r="AD46" s="9"/>
+      <c r="AE46" s="9"/>
+      <c r="AF46" s="9"/>
+      <c r="AG46" s="9"/>
+      <c r="AH46" s="9"/>
+      <c r="AI46" s="9"/>
+      <c r="AJ46" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK46,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK46" s="9"/>
+      <c r="AL46" s="9"/>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A47" s="9"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+      <c r="Y47" s="9"/>
+      <c r="Z47" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y47,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA47" s="9"/>
+      <c r="AB47" s="9"/>
+      <c r="AC47" s="9"/>
+      <c r="AD47" s="9"/>
+      <c r="AE47" s="9"/>
+      <c r="AF47" s="9"/>
+      <c r="AG47" s="9"/>
+      <c r="AH47" s="9"/>
+      <c r="AI47" s="9"/>
+      <c r="AJ47" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK47,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK47" s="9"/>
+      <c r="AL47" s="9"/>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A48" s="9"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9"/>
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9"/>
+      <c r="R48" s="9"/>
+      <c r="S48" s="9"/>
+      <c r="T48" s="9"/>
+      <c r="U48" s="9"/>
+      <c r="V48" s="9"/>
+      <c r="W48" s="9"/>
+      <c r="X48" s="9"/>
+      <c r="Y48" s="9"/>
+      <c r="Z48" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y48,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA48" s="9"/>
+      <c r="AB48" s="9"/>
+      <c r="AC48" s="9"/>
+      <c r="AD48" s="9"/>
+      <c r="AE48" s="9"/>
+      <c r="AF48" s="9"/>
+      <c r="AG48" s="9"/>
+      <c r="AH48" s="9"/>
+      <c r="AI48" s="9"/>
+      <c r="AJ48" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK48,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK48" s="9"/>
+      <c r="AL48" s="9"/>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A49" s="9"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="9"/>
+      <c r="S49" s="9"/>
+      <c r="T49" s="9"/>
+      <c r="U49" s="9"/>
+      <c r="V49" s="9"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="9"/>
+      <c r="Z49" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y49,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA49" s="9"/>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9"/>
+      <c r="AD49" s="9"/>
+      <c r="AE49" s="9"/>
+      <c r="AF49" s="9"/>
+      <c r="AG49" s="9"/>
+      <c r="AH49" s="9"/>
+      <c r="AI49" s="9"/>
+      <c r="AJ49" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK49,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK49" s="9"/>
+      <c r="AL49" s="9"/>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.35">
+      <c r="A50" s="9"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="9"/>
+      <c r="O50" s="9"/>
+      <c r="P50" s="9"/>
+      <c r="Q50" s="9"/>
+      <c r="R50" s="9"/>
+      <c r="S50" s="9"/>
+      <c r="T50" s="9"/>
+      <c r="U50" s="9"/>
+      <c r="V50" s="9"/>
+      <c r="W50" s="9"/>
+      <c r="X50" s="9"/>
+      <c r="Y50" s="9"/>
+      <c r="Z50" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(Y50,'[1]Listados Codigos'!$EB$2:$EC$20,2,0),"Vacio")</f>
+        <v>Vacio</v>
+      </c>
+      <c r="AA50" s="9"/>
+      <c r="AB50" s="9"/>
+      <c r="AC50" s="9"/>
+      <c r="AD50" s="9"/>
+      <c r="AE50" s="9"/>
+      <c r="AF50" s="9"/>
+      <c r="AG50" s="9"/>
+      <c r="AH50" s="9"/>
+      <c r="AI50" s="9"/>
+      <c r="AJ50" s="29" t="str">
+        <f>+IFERROR(VLOOKUP(AK50,'[1]Listados Codigos'!$EG$2:$EH$33,2,0),"")</f>
+        <v/>
+      </c>
+      <c r="AK50" s="9"/>
+      <c r="AL50" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="Y1:AB1"/>
+    <mergeCell ref="AC1:AI1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="AJ1:AL1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="7f926d49-af99-4164-9d27-b8d68a460b5b" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="713a9ea8-b2f7-4fde-95a3-c03760906699">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010003FD7FC88BEAB046B90D691935AD7053" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ff5436e847ef4329f1af97b909cbb985">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7f926d49-af99-4164-9d27-b8d68a460b5b" xmlns:ns3="713a9ea8-b2f7-4fde-95a3-c03760906699" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ef12fbe9b907378684d7c11ec79f8e8" ns2:_="" ns3:_="">
     <xsd:import namespace="7f926d49-af99-4164-9d27-b8d68a460b5b"/>
@@ -6866,7 +11683,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6875,18 +11692,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="7f926d49-af99-4164-9d27-b8d68a460b5b" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="713a9ea8-b2f7-4fde-95a3-c03760906699">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35CA4BBC-6732-468A-AFBB-6883143AD71D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7f926d49-af99-4164-9d27-b8d68a460b5b"/>
+    <ds:schemaRef ds:uri="713a9ea8-b2f7-4fde-95a3-c03760906699"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BBB629E-D2E3-4B94-9001-74538279B499}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6905,21 +11722,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E64858C-1575-4C64-B3B9-928DFD164BC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35CA4BBC-6732-468A-AFBB-6883143AD71D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7f926d49-af99-4164-9d27-b8d68a460b5b"/>
-    <ds:schemaRef ds:uri="713a9ea8-b2f7-4fde-95a3-c03760906699"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>